--- a/src/arm/stagiaires.xlsx
+++ b/src/arm/stagiaires.xlsx
@@ -398,21 +398,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BN35"/>
+  <dimension ref="A1:BN23"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="39.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="8" max="8" width="13.83203125" customWidth="1"/>
     <col min="9" max="9" width="59.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="16.83203125" customWidth="1"/>
     <col min="12" max="12" width="21.83203125" customWidth="1"/>
-    <col min="13" max="13" width="25.83203125" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" customWidth="1"/>
     <col min="14" max="14" width="8.83203125" customWidth="1"/>
     <col min="15" max="15" width="20.83203125" customWidth="1"/>
     <col min="16" max="16" width="5.83203125" customWidth="1"/>
@@ -422,17 +422,17 @@
     <col min="20" max="20" width="21.83203125" customWidth="1"/>
     <col min="21" max="21" width="13.83203125" customWidth="1"/>
     <col min="22" max="22" width="28.83203125" customWidth="1"/>
-    <col min="23" max="23" width="43.83203125" customWidth="1"/>
+    <col min="23" max="23" width="32.83203125" customWidth="1"/>
     <col min="24" max="24" width="13.83203125" customWidth="1"/>
     <col min="25" max="25" width="27.83203125" customWidth="1"/>
     <col min="26" max="26" width="5.83203125" customWidth="1"/>
     <col min="27" max="27" width="10.83203125" customWidth="1"/>
     <col min="28" max="28" width="5.83203125" customWidth="1"/>
-    <col min="29" max="29" width="20.83203125" customWidth="1"/>
-    <col min="30" max="30" width="22.83203125" customWidth="1"/>
+    <col min="29" max="29" width="13.83203125" customWidth="1"/>
+    <col min="30" max="30" width="19.83203125" customWidth="1"/>
     <col min="31" max="31" width="28.83203125" customWidth="1"/>
     <col min="32" max="32" width="5.83203125" customWidth="1"/>
-    <col min="33" max="33" width="10.83203125" customWidth="1"/>
+    <col min="33" max="33" width="6.83203125" customWidth="1"/>
     <col min="34" max="34" width="33.83203125" customWidth="1"/>
     <col min="35" max="35" width="21.83203125" customWidth="1"/>
     <col min="36" max="36" width="22.83203125" customWidth="1"/>
@@ -447,15 +447,15 @@
     <col min="45" max="45" width="22.83203125" customWidth="1"/>
     <col min="46" max="46" width="16.83203125" customWidth="1"/>
     <col min="47" max="47" width="68.83203125" customWidth="1"/>
-    <col min="48" max="48" width="60.83203125" customWidth="1"/>
+    <col min="48" max="48" width="50.83203125" customWidth="1"/>
     <col min="49" max="49" width="22.83203125" customWidth="1"/>
     <col min="50" max="50" width="68.83203125" customWidth="1"/>
     <col min="51" max="51" width="38.83203125" customWidth="1"/>
     <col min="52" max="52" width="27.83203125" customWidth="1"/>
     <col min="53" max="53" width="28.83203125" customWidth="1"/>
-    <col min="54" max="54" width="120.83203125" customWidth="1"/>
+    <col min="54" max="54" width="25.83203125" customWidth="1"/>
     <col min="55" max="55" width="28.83203125" customWidth="1"/>
-    <col min="56" max="56" width="51.83203125" customWidth="1"/>
+    <col min="56" max="56" width="44.83203125" customWidth="1"/>
     <col min="57" max="57" width="31.83203125" customWidth="1"/>
     <col min="58" max="58" width="29.83203125" customWidth="1"/>
     <col min="59" max="59" width="24.83203125" customWidth="1"/>
@@ -465,7 +465,7 @@
     <col min="63" max="63" width="25.83203125" customWidth="1"/>
     <col min="64" max="64" width="28.83203125" customWidth="1"/>
     <col min="65" max="65" width="33.83203125" customWidth="1"/>
-    <col min="66" max="66" width="148.83203125" customWidth="1"/>
+    <col min="66" max="66" width="151.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -670,22 +670,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>137163</v>
+        <v>140685</v>
       </c>
       <c r="B2" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C2" t="str">
-        <v>GOUMAN</v>
+        <v>CASIEZ</v>
       </c>
       <c r="D2" t="str">
-        <v>Maxime</v>
+        <v>Jehanne</v>
       </c>
       <c r="E2" t="str">
-        <v>m.gouman@e2c-grandlille.fr</v>
+        <v>j.casiez@e2c-grandlille.fr</v>
       </c>
       <c r="F2" t="str">
-        <v>07 66 75 78 57</v>
+        <v>07 66 24 36 41</v>
       </c>
       <c r="G2" t="str">
         <v>Grand Lille</v>
@@ -693,17 +693,17 @@
       <c r="H2" t="str">
         <v>Armentières</v>
       </c>
-      <c r="K2" t="str">
-        <v>Je sais</v>
+      <c r="I2" t="str">
+        <v>Assistant maternel agréé / Assistante maternelle agréée</v>
       </c>
       <c r="L2" t="str">
-        <v>référés Jérôme</v>
+        <v>référés Delphine P.</v>
       </c>
       <c r="M2" t="str">
-        <v>2605/mai 2026 ARM</v>
+        <v>2606/juin 2026 ARM</v>
       </c>
       <c r="O2" t="str">
-        <v>BOLPAIRE Jérôme</v>
+        <v>PASQUIER Delphine</v>
       </c>
       <c r="P2">
         <v>20</v>
@@ -712,22 +712,25 @@
         <v>20</v>
       </c>
       <c r="R2" s="1">
-        <v>38639</v>
+        <v>38743</v>
       </c>
       <c r="T2" t="str">
-        <v>Tourcoing</v>
+        <v>Beuvry</v>
       </c>
       <c r="U2" t="str">
         <v>FRANCAISE</v>
       </c>
+      <c r="V2" t="str">
+        <v>OUI</v>
+      </c>
       <c r="W2" t="str">
-        <v>69 Rue des Pretres</v>
+        <v>1192 Rue de Loisne</v>
       </c>
       <c r="X2" t="str">
-        <v>59660</v>
+        <v>62136</v>
       </c>
       <c r="Y2" t="str">
-        <v>Merville</v>
+        <v>Vieille-Chapelle</v>
       </c>
       <c r="Z2" t="str">
         <v>Non</v>
@@ -739,7 +742,7 @@
         <v>NON</v>
       </c>
       <c r="AD2" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE2" t="str">
         <v>Non</v>
@@ -760,69 +763,84 @@
         <v>Non</v>
       </c>
       <c r="AK2" t="str">
-        <v>65h30m</v>
+        <v>111h30m</v>
       </c>
       <c r="AL2" t="str">
-        <v>0m</v>
+        <v>32h</v>
       </c>
       <c r="AM2" t="str">
-        <v>9h45m</v>
+        <v>4h45m</v>
       </c>
       <c r="AN2" s="1">
-        <v>46160.38820601852</v>
+        <v>46195.37998842593</v>
       </c>
       <c r="AP2" s="1">
-        <v>46436.38611111111</v>
+        <v>46468.66111111111</v>
       </c>
       <c r="AU2" s="1">
-        <v>46140.575694444444</v>
+        <v>46185.66875</v>
       </c>
       <c r="AV2" t="str">
-        <v>MISSION LOCALE DE FLANDRE INTERIEURE</v>
+        <v>MISSION LOCALE DE L'ARTOIS - Antenne de LAVENTIE</v>
       </c>
       <c r="AW2" t="str">
-        <v>Nadège Douchet</v>
+        <v>Jordan Taffin</v>
       </c>
       <c r="AX2" s="1">
-        <v>46140.3875</v>
+        <v>46185.384722222225</v>
+      </c>
+      <c r="AY2" t="str">
+        <v>jordan.taffin@mlartois.org</v>
+      </c>
+      <c r="AZ2" t="str">
+        <v>0321644940</v>
       </c>
       <c r="BA2" t="str">
         <v>NON</v>
       </c>
+      <c r="BG2" t="str">
+        <v>19408</v>
+      </c>
+      <c r="BH2" s="1">
+        <v>45961.041666666664</v>
+      </c>
+      <c r="BI2" t="str">
+        <v>1753085C</v>
+      </c>
       <c r="BJ2" t="str">
-        <v>fef70ae7-776c-46db-b1eb-c236069a658a</v>
+        <v>18325e81-95fc-410a-a343-96b5010c14b9</v>
       </c>
       <c r="BK2" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL2" t="str">
         <v/>
       </c>
       <c r="BM2" t="str">
-        <v>maximegouman703@gmail.com</v>
+        <v>jehanne.casiez@gmail.com</v>
       </c>
       <c r="BN2" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/j_casiez_e2c-grandlille_fr/IgAlW6OzhawNQJ6m67T1KhavAcsjjxUums-vfQ8L1oC16tI?e=72yBNa</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>137159</v>
+        <v>140658</v>
       </c>
       <c r="B3" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C3" t="str">
-        <v>DOUDAI</v>
+        <v>ANCIEUX</v>
       </c>
       <c r="D3" t="str">
-        <v>Ambrine</v>
+        <v>Nicolas</v>
       </c>
       <c r="E3" t="str">
-        <v>a.doudai@e2c-grandlille.fr</v>
+        <v>n.ancieux@e2c-grandlille.fr</v>
       </c>
       <c r="F3" t="str">
-        <v>07 73 90 18 70</v>
+        <v xml:space="preserve">06 09 95 35 17 </v>
       </c>
       <c r="G3" t="str">
         <v>Grand Lille</v>
@@ -830,50 +848,35 @@
       <c r="H3" t="str">
         <v>Armentières</v>
       </c>
-      <c r="I3" t="str">
-        <v>Assistant / Assistante de gestion en ressources humaines</v>
-      </c>
-      <c r="K3" t="str">
-        <v>J'ai des idées</v>
-      </c>
       <c r="L3" t="str">
-        <v>référés Gérard</v>
+        <v>référés Coralie</v>
       </c>
       <c r="M3" t="str">
-        <v>2605/mai 2026 ARM</v>
+        <v>2606/juin 2026 ARM</v>
       </c>
       <c r="O3" t="str">
-        <v>NOWINSKI Gérard</v>
+        <v>BENKHALIL Coralie</v>
       </c>
       <c r="P3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R3" s="1">
-        <v>39017</v>
+        <v>37855</v>
       </c>
       <c r="T3" t="str">
-        <v>Maubeuge</v>
+        <v>Armentières</v>
       </c>
       <c r="U3" t="str">
         <v>FRANCAISE</v>
       </c>
-      <c r="W3" t="str">
-        <v>3b Rue du Marechal Joffre</v>
-      </c>
-      <c r="X3" t="str">
-        <v>59280</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>Armentières</v>
+      <c r="V3" t="str">
+        <v>OUI</v>
       </c>
       <c r="Z3" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>QN05968M</v>
+        <v>Non</v>
       </c>
       <c r="AB3" t="str">
         <v>Non</v>
@@ -882,7 +885,7 @@
         <v>NON</v>
       </c>
       <c r="AD3" t="str">
-        <v>4 validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE3" t="str">
         <v>Non</v>
@@ -891,7 +894,7 @@
         <v>Non</v>
       </c>
       <c r="AG3" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH3" t="str">
         <v>Non</v>
@@ -903,78 +906,75 @@
         <v>Non</v>
       </c>
       <c r="AK3" t="str">
-        <v>69h15m</v>
+        <v>113h</v>
       </c>
       <c r="AL3" t="str">
-        <v>0m</v>
+        <v>28h</v>
       </c>
       <c r="AM3" t="str">
-        <v>9h45m</v>
+        <v>3h15m</v>
       </c>
       <c r="AN3" s="1">
-        <v>46160.384247685186</v>
+        <v>46195.37762731482</v>
       </c>
       <c r="AP3" s="1">
-        <v>46436.38263888889</v>
+        <v>46468.589583333334</v>
       </c>
       <c r="AU3" s="1">
-        <v>46140.55902777778</v>
+        <v>46189.61597222222</v>
       </c>
       <c r="AV3" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW3" t="str">
-        <v>Magali Dutoit</v>
+        <v>En direct</v>
       </c>
       <c r="AX3" s="1">
-        <v>46140.56041666667</v>
+        <v>46185.61388888889</v>
       </c>
       <c r="BA3" t="str">
         <v>NON</v>
       </c>
       <c r="BG3" t="str">
-        <v>17797</v>
+        <v>19402</v>
       </c>
       <c r="BH3" s="1">
-        <v>45923.083333333336</v>
+        <v>46086.041666666664</v>
       </c>
       <c r="BI3" t="str">
-        <v>5944562F</v>
+        <v>5730821D</v>
       </c>
       <c r="BJ3" t="str">
-        <v>b9cf2539-74f6-42ee-9dbc-9d70cc79c13f</v>
+        <v>41bcfe0f-6071-402d-9d0c-cb0cc63560ab</v>
       </c>
       <c r="BK3" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL3" t="str">
         <v/>
       </c>
       <c r="BM3" t="str">
-        <v>doudai59280@gmail.com</v>
+        <v>ancieuxnicolas59116@gmail.com</v>
       </c>
       <c r="BN3" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/n_ancieux_e2c-grandlille_fr/IgBliXHyHa34RKhIdsQ-G-0iAQDwl3Bi7-ZXqfhPjFyjFW0?e=jgeOEg</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>135785</v>
+        <v>140393</v>
       </c>
       <c r="B4" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C4" t="str">
-        <v>MONFLIER</v>
+        <v xml:space="preserve"> SENGEZ VANDYCKE</v>
       </c>
       <c r="D4" t="str">
-        <v>Raphaël</v>
+        <v>Sophie</v>
       </c>
       <c r="E4" t="str">
-        <v>r.monflier@e2c-grandlille.fr</v>
+        <v>s.vandycke@e2c-grandlille.fr</v>
       </c>
       <c r="F4" t="str">
-        <v>06 12 42 85 11</v>
+        <v>07 82 58 08 87</v>
       </c>
       <c r="G4" t="str">
         <v>Grand Lille</v>
@@ -982,29 +982,26 @@
       <c r="H4" t="str">
         <v>Armentières</v>
       </c>
-      <c r="K4" t="str">
-        <v>J'ai des idées</v>
-      </c>
       <c r="L4" t="str">
-        <v>référés Delphine P.</v>
+        <v>référés Gérard</v>
       </c>
       <c r="M4" t="str">
-        <v>2605/mai 2026 ARM</v>
+        <v>2606/juin 2026 ARM</v>
       </c>
       <c r="O4" t="str">
-        <v>PASQUIER Delphine</v>
+        <v>NOWINSKI Gérard</v>
       </c>
       <c r="P4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="R4" s="1">
-        <v>38619</v>
+        <v>40066</v>
       </c>
       <c r="T4" t="str">
-        <v>Hazebrouck</v>
+        <v>Armentières</v>
       </c>
       <c r="U4" t="str">
         <v>FRANCAISE</v>
@@ -1013,10 +1010,10 @@
         <v>OUI</v>
       </c>
       <c r="X4" t="str">
-        <v>59270</v>
+        <v>59850</v>
       </c>
       <c r="Y4" t="str">
-        <v>Bailleul</v>
+        <v>Nieppe</v>
       </c>
       <c r="Z4" t="str">
         <v>Non</v>
@@ -1028,7 +1025,7 @@
         <v>NON</v>
       </c>
       <c r="AD4" t="str">
-        <v>3 non validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE4" t="str">
         <v>Non</v>
@@ -1037,7 +1034,7 @@
         <v>Non</v>
       </c>
       <c r="AG4" t="str">
-        <v>AVEC</v>
+        <v>SANS</v>
       </c>
       <c r="AH4" t="str">
         <v>Non</v>
@@ -1049,84 +1046,99 @@
         <v>Non</v>
       </c>
       <c r="AK4" t="str">
-        <v>75h15m</v>
+        <v>64h15m</v>
       </c>
       <c r="AL4" t="str">
-        <v>0m</v>
+        <v>33h30m</v>
       </c>
       <c r="AM4" t="str">
-        <v>0m</v>
+        <v>52h</v>
       </c>
       <c r="AN4" s="1">
-        <v>46160.38931712963</v>
+        <v>46195.37390046296</v>
       </c>
       <c r="AP4" s="1">
-        <v>46436.388194444444</v>
+        <v>46468.66388888889</v>
       </c>
       <c r="AU4" s="1">
-        <v>46140.34444444445</v>
+        <v>46182.67083333333</v>
       </c>
       <c r="AV4" t="str">
-        <v>LA SPRENE - Merville</v>
+        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
       </c>
       <c r="AW4" t="str">
-        <v>Eden Fontaine</v>
+        <v>Manon Dien</v>
       </c>
       <c r="AX4" s="1">
-        <v>46111.34652777778</v>
+        <v>46188.37291666667</v>
       </c>
       <c r="AY4" t="str">
-        <v>etayage.flandre@sprene.fr</v>
+        <v>mdien@aefavl.fr</v>
       </c>
       <c r="AZ4" t="str">
-        <v>0608568569</v>
+        <v>0320109220</v>
       </c>
       <c r="BA4" t="str">
         <v>NON</v>
       </c>
+      <c r="BB4" t="str">
+        <v>VANDYCKE</v>
+      </c>
+      <c r="BC4" t="str">
+        <v>Dorothée</v>
+      </c>
+      <c r="BD4" t="str">
+        <v>16 Bât Artois Rue des Sources 59850 NIEPPE</v>
+      </c>
+      <c r="BE4" t="str">
+        <v>0668399597</v>
+      </c>
+      <c r="BF4" t="str">
+        <v>doro59850@hotmail.fr</v>
+      </c>
       <c r="BG4" t="str">
-        <v>17523</v>
+        <v>19412</v>
       </c>
       <c r="BH4" s="1">
-        <v>46155.083333333336</v>
+        <v>46105.041666666664</v>
       </c>
       <c r="BI4" t="str">
-        <v>5834701s</v>
+        <v>598962H</v>
       </c>
       <c r="BJ4" t="str">
-        <v>a25af803-b316-4ce2-ba35-0f9aacb48f75</v>
+        <v>e9212490-07fa-437a-9e53-ec632a4efbc3</v>
       </c>
       <c r="BK4" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL4" t="str">
         <v/>
       </c>
       <c r="BM4" t="str">
-        <v>raphaelmonflier@gmail.com</v>
+        <v>sengezsophie10@gmail.com</v>
       </c>
       <c r="BN4" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_vandycke_e2c-grandlille_fr/IgANFhAHHvBHRLMR-I0zY6lqARNdb9AuCYf_VOJMu99fub0?e=oqdwQJ</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>135784</v>
+        <v>137163</v>
       </c>
       <c r="B5" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C5" t="str">
-        <v>EL FARAJ--GONZALEZ-DOMINGUEZ</v>
+        <v>GOUMAN</v>
       </c>
       <c r="D5" t="str">
-        <v>Nina</v>
+        <v>Maxime</v>
       </c>
       <c r="E5" t="str">
-        <v>n.gonzalesdominguez@e2c-grandlille.fr</v>
+        <v>m.gouman@e2c-grandlille.fr</v>
       </c>
       <c r="F5" t="str">
-        <v>07 81 37 09 92</v>
+        <v>07 66 75 78 57</v>
       </c>
       <c r="G5" t="str">
         <v>Grand Lille</v>
@@ -1135,43 +1147,43 @@
         <v>Armentières</v>
       </c>
       <c r="K5" t="str">
-        <v>J'explore</v>
+        <v>Je sais</v>
       </c>
       <c r="L5" t="str">
-        <v>référés Delphine P.</v>
+        <v>référés Jérôme</v>
       </c>
       <c r="M5" t="str">
         <v>2605/mai 2026 ARM</v>
       </c>
       <c r="O5" t="str">
-        <v>PASQUIER Delphine</v>
+        <v>BOLPAIRE Jérôme</v>
       </c>
       <c r="P5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R5" s="1">
-        <v>39143</v>
+        <v>38639</v>
       </c>
       <c r="T5" t="str">
-        <v>Paris 20ème</v>
+        <v>Tourcoing</v>
       </c>
       <c r="U5" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="V5" t="str">
-        <v>NON</v>
+        <v>OUI</v>
       </c>
       <c r="W5" t="str">
-        <v>195B Rue du General Leclerc</v>
+        <v>69 Rue des Pretres</v>
       </c>
       <c r="X5" t="str">
-        <v>59280</v>
+        <v>59660</v>
       </c>
       <c r="Y5" t="str">
-        <v>Armentières</v>
+        <v>Merville</v>
       </c>
       <c r="Z5" t="str">
         <v>Non</v>
@@ -1183,7 +1195,7 @@
         <v>NON</v>
       </c>
       <c r="AD5" t="str">
-        <v>3 non validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE5" t="str">
         <v>Non</v>
@@ -1204,66 +1216,87 @@
         <v>Non</v>
       </c>
       <c r="AK5" t="str">
-        <v>74h15m</v>
+        <v>105h</v>
       </c>
       <c r="AL5" t="str">
-        <v>0m</v>
+        <v>92h30m</v>
       </c>
       <c r="AM5" t="str">
-        <v>3h15m</v>
+        <v>85h30m</v>
       </c>
       <c r="AN5" s="1">
-        <v>46160.39306712963</v>
+        <v>46160.38820601852</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>46203.61863425926</v>
       </c>
       <c r="AP5" s="1">
-        <v>46436.38402777778</v>
+        <v>46436.38611111111</v>
       </c>
       <c r="AU5" s="1">
-        <v>46126.342361111114</v>
+        <v>46140.575694444444</v>
       </c>
       <c r="AV5" t="str">
-        <v>En direct</v>
+        <v>MISSION LOCALE DE FLANDRE INTERIEURE</v>
+      </c>
+      <c r="AW5" t="str">
+        <v>Nadège Douchet</v>
       </c>
       <c r="AX5" s="1">
-        <v>46119.384722222225</v>
+        <v>46140.3875</v>
+      </c>
+      <c r="AY5" t="str">
+        <v>n.douchet@aeffi.fr</v>
+      </c>
+      <c r="AZ5" t="str">
+        <v>0328503801</v>
       </c>
       <c r="BA5" t="str">
         <v>NON</v>
       </c>
+      <c r="BG5" t="str">
+        <v>18121</v>
+      </c>
+      <c r="BH5" s="1">
+        <v>45825.083333333336</v>
+      </c>
+      <c r="BI5" t="str">
+        <v>5777603D</v>
+      </c>
       <c r="BJ5" t="str">
-        <v>a7a8a4fd-7f5c-466b-b700-3b4c088a10a1</v>
+        <v>fef70ae7-776c-46db-b1eb-c236069a658a</v>
       </c>
       <c r="BK5" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL5" t="str">
         <v/>
       </c>
       <c r="BM5" t="str">
-        <v>gonzales_dominguez02@outlook.fr</v>
+        <v>maximegouman703@gmail.com</v>
       </c>
       <c r="BN5" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_gouman_e2c-grandlille_fr/IgD1e1crCmL5Q4-CWTrxMk6TAVKN5VXjr5ieZj_oHmsZxxw?e=gVxuAv</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>131806</v>
+        <v>137159</v>
       </c>
       <c r="B6" t="str">
         <v>Femme</v>
       </c>
       <c r="C6" t="str">
-        <v>CAPON</v>
+        <v>DOUDAI</v>
       </c>
       <c r="D6" t="str">
-        <v>Marie</v>
+        <v>Ambrine</v>
       </c>
       <c r="E6" t="str">
-        <v>m.capon@e2c-grandlille.fr</v>
+        <v>a.doudai@e2c-grandlille.fr</v>
       </c>
       <c r="F6" t="str">
-        <v>06 38 15 01 68</v>
+        <v>07 73 90 18 70</v>
       </c>
       <c r="G6" t="str">
         <v>Grand Lille</v>
@@ -1271,35 +1304,38 @@
       <c r="H6" t="str">
         <v>Armentières</v>
       </c>
+      <c r="I6" t="str">
+        <v>Assistant / Assistante de gestion en ressources humaines</v>
+      </c>
       <c r="K6" t="str">
-        <v>J'explore</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L6" t="str">
-        <v>référés Delphine P.</v>
+        <v>référés Gérard</v>
       </c>
       <c r="M6" t="str">
         <v>2605/mai 2026 ARM</v>
       </c>
       <c r="O6" t="str">
-        <v>PASQUIER Delphine</v>
+        <v>NOWINSKI Gérard</v>
       </c>
       <c r="P6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R6" s="1">
-        <v>39825</v>
+        <v>39017</v>
       </c>
       <c r="T6" t="str">
-        <v>Cambrai</v>
+        <v>Maubeuge</v>
       </c>
       <c r="U6" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="W6" t="str">
-        <v>37 Rue de la Cite</v>
+        <v>3b Rue du Marechal Joffre</v>
       </c>
       <c r="X6" t="str">
         <v>59280</v>
@@ -1308,7 +1344,10 @@
         <v>Armentières</v>
       </c>
       <c r="Z6" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>QN05968M</v>
       </c>
       <c r="AB6" t="str">
         <v>Non</v>
@@ -1317,7 +1356,7 @@
         <v>NON</v>
       </c>
       <c r="AD6" t="str">
-        <v>3 non validé</v>
+        <v>4 validé</v>
       </c>
       <c r="AE6" t="str">
         <v>Non</v>
@@ -1338,99 +1377,87 @@
         <v>Non</v>
       </c>
       <c r="AK6" t="str">
-        <v>69h30m</v>
+        <v>197h</v>
       </c>
       <c r="AL6" t="str">
-        <v>0m</v>
+        <v>98h</v>
       </c>
       <c r="AM6" t="str">
-        <v>9h45m</v>
+        <v>16h15m</v>
       </c>
       <c r="AN6" s="1">
-        <v>46160.38075231481</v>
+        <v>46160.384247685186</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>46202.61875</v>
       </c>
       <c r="AP6" s="1">
-        <v>46436.43125</v>
+        <v>46436.38263888889</v>
       </c>
       <c r="AU6" s="1">
-        <v>46105.384722222225</v>
+        <v>46140.55902777778</v>
       </c>
       <c r="AV6" t="str">
         <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
       </c>
       <c r="AW6" t="str">
-        <v>Bouton Christelle</v>
+        <v>Magali Dutoit</v>
       </c>
       <c r="AX6" s="1">
-        <v>46101.38611111111</v>
+        <v>46140.56041666667</v>
       </c>
       <c r="AY6" t="str">
-        <v>cbouton@aefavl.fr</v>
+        <v>mdutoit@aefavl.fr</v>
       </c>
       <c r="AZ6" t="str">
         <v>0320109220</v>
       </c>
       <c r="BA6" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB6" t="str">
-        <v>CAPON</v>
-      </c>
-      <c r="BC6" t="str">
-        <v>Jean Michel et Cécile</v>
-      </c>
-      <c r="BD6" t="str">
-        <v>37 Rue de la Cité 59280 Armentières</v>
-      </c>
-      <c r="BE6" t="str">
-        <v>0671990029</v>
-      </c>
-      <c r="BF6" t="str">
-        <v>jean-michelcapon@sfr.fr</v>
+        <v>NON</v>
       </c>
       <c r="BG6" t="str">
-        <v>17724</v>
+        <v>17797</v>
       </c>
       <c r="BH6" s="1">
-        <v>45993.041666666664</v>
+        <v>45923.083333333336</v>
       </c>
       <c r="BI6" t="str">
-        <v>5965657K</v>
+        <v>5944562F</v>
       </c>
       <c r="BJ6" t="str">
-        <v>e194023d-d14a-44ef-a8f9-c3e7d69dce60</v>
+        <v>b9cf2539-74f6-42ee-9dbc-9d70cc79c13f</v>
       </c>
       <c r="BK6" t="str">
-        <v>PendingAcceptance</v>
+        <v>Accepted</v>
       </c>
       <c r="BL6" t="str">
         <v/>
       </c>
       <c r="BM6" t="str">
-        <v>mariecapon0@gmail.com</v>
+        <v>doudai59280@gmail.com</v>
       </c>
       <c r="BN6" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/a_doudai_e2c-grandlille_fr/IgAlhbmLsKNuRKdpXQKU5WWdAVsPwEDgd0M1749DF26q4rM?e=ogaF3Y</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>82206</v>
+        <v>135785</v>
       </c>
       <c r="B7" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C7" t="str">
-        <v>ARIIPEU</v>
+        <v>MONFLIER</v>
       </c>
       <c r="D7" t="str">
-        <v>Taïna</v>
+        <v>Raphaël</v>
       </c>
       <c r="E7" t="str">
-        <v>t.ariipeu@e2c-grandlille.fr</v>
+        <v>r.monflier@e2c-grandlille.fr</v>
       </c>
       <c r="F7" t="str">
-        <v>06 12 37 02 70</v>
+        <v>06 12 42 85 11</v>
       </c>
       <c r="G7" t="str">
         <v>Grand Lille</v>
@@ -1438,32 +1465,29 @@
       <c r="H7" t="str">
         <v>Armentières</v>
       </c>
-      <c r="I7" t="str">
-        <v>Maître / Maîtresse de cérémonie funéraire</v>
-      </c>
       <c r="K7" t="str">
-        <v>J'y vais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L7" t="str">
-        <v>référés Gérard</v>
+        <v>référés Delphine P.</v>
       </c>
       <c r="M7" t="str">
-        <v>2603/mars 2026 ARM</v>
+        <v>2605/mai 2026 ARM</v>
       </c>
       <c r="O7" t="str">
-        <v>NOWINSKI Gérard</v>
+        <v>PASQUIER Delphine</v>
       </c>
       <c r="P7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R7" s="1">
-        <v>38100</v>
+        <v>38619</v>
       </c>
       <c r="T7" t="str">
-        <v>Saint Quentin</v>
+        <v>Hazebrouck</v>
       </c>
       <c r="U7" t="str">
         <v>FRANCAISE</v>
@@ -1471,14 +1495,11 @@
       <c r="V7" t="str">
         <v>OUI</v>
       </c>
-      <c r="W7" t="str">
-        <v>46 Rue Brune</v>
-      </c>
       <c r="X7" t="str">
-        <v>59116</v>
+        <v>59270</v>
       </c>
       <c r="Y7" t="str">
-        <v>Houplines</v>
+        <v>Bailleul</v>
       </c>
       <c r="Z7" t="str">
         <v>Non</v>
@@ -1490,7 +1511,7 @@
         <v>NON</v>
       </c>
       <c r="AD7" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE7" t="str">
         <v>Non</v>
@@ -1499,7 +1520,7 @@
         <v>Non</v>
       </c>
       <c r="AG7" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH7" t="str">
         <v>Non</v>
@@ -1511,55 +1532,55 @@
         <v>Non</v>
       </c>
       <c r="AK7" t="str">
-        <v>171h45m</v>
+        <v>177h45m</v>
       </c>
       <c r="AL7" t="str">
-        <v>168h</v>
+        <v>105h</v>
       </c>
       <c r="AM7" t="str">
-        <v>61h30m</v>
+        <v>29h</v>
       </c>
       <c r="AN7" s="1">
-        <v>46090.373611111114</v>
+        <v>46160.38931712963</v>
       </c>
       <c r="AO7" s="1">
-        <v>46139.46055555555</v>
+        <v>46202.61666666667</v>
       </c>
       <c r="AP7" s="1">
-        <v>46365.45763888889</v>
+        <v>46436.388194444444</v>
       </c>
       <c r="AU7" s="1">
-        <v>45944.43402777778</v>
+        <v>46140.34444444445</v>
       </c>
       <c r="AV7" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
+        <v>LA SPRENE - Merville</v>
       </c>
       <c r="AW7" t="str">
-        <v>DERYCKERE Antoine</v>
+        <v>Eden Fontaine</v>
       </c>
       <c r="AX7" s="1">
-        <v>45939.436111111114</v>
+        <v>46111.34652777778</v>
       </c>
       <c r="AY7" t="str">
-        <v>aderyckere@aefavl.fr</v>
+        <v>etayage.flandre@sprene.fr</v>
       </c>
       <c r="AZ7" t="str">
-        <v>0320109220</v>
+        <v>0608568569</v>
       </c>
       <c r="BA7" t="str">
         <v>NON</v>
       </c>
       <c r="BG7" t="str">
-        <v>11294</v>
+        <v>17253</v>
       </c>
       <c r="BH7" s="1">
-        <v>45909.083333333336</v>
+        <v>46155.083333333336</v>
       </c>
       <c r="BI7" t="str">
-        <v>5770540B</v>
+        <v>5834701s</v>
       </c>
       <c r="BJ7" t="str">
-        <v>2a50664a-c78b-4a5f-a898-1a105c4fe4b2</v>
+        <v>a25af803-b316-4ce2-ba35-0f9aacb48f75</v>
       </c>
       <c r="BK7" t="str">
         <v>Accepted</v>
@@ -1568,30 +1589,30 @@
         <v/>
       </c>
       <c r="BM7" t="str">
-        <v>t.ariipeu@e2c-grandlille.fr</v>
+        <v>raphaelmonflier@gmail.com</v>
       </c>
       <c r="BN7" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/t_ariipeu_e2c-grandlille_fr/IgB68KulNlunQ7V_Bit0a9OCATMJUuLMSmezJ-xppAw1pLU?e=yjPNOa</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/r_monflier_e2c-grandlille_fr/IgBSPRLbF627QaVYa6tNoN9TARAbqTOi0_cbl9Zpu-1rL2o?e=Kcnbwp</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>78277</v>
+        <v>135784</v>
       </c>
       <c r="B8" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C8" t="str">
-        <v>DUBOIS</v>
+        <v>EL FARAJ--GONZALEZ-DOMINGUEZ</v>
       </c>
       <c r="D8" t="str">
-        <v>Honny</v>
+        <v>Nina</v>
       </c>
       <c r="E8" t="str">
-        <v>h.dubois@e2c-grandlille.fr</v>
+        <v>n.gonzalesdominguez@e2c-grandlille.fr</v>
       </c>
       <c r="F8" t="str">
-        <v>06 19 74 75 61</v>
+        <v>07 81 37 09 92</v>
       </c>
       <c r="G8" t="str">
         <v>Grand Lille</v>
@@ -1600,43 +1621,46 @@
         <v>Armentières</v>
       </c>
       <c r="I8" t="str">
-        <v>Employé / Employée de libre-service</v>
+        <v>Aide aux personnes âgées</v>
       </c>
       <c r="K8" t="str">
         <v>J'explore</v>
       </c>
       <c r="L8" t="str">
-        <v>référés Coralie</v>
+        <v>référés Delphine P.</v>
       </c>
       <c r="M8" t="str">
-        <v>2604/avril 2026 ARM</v>
+        <v>2605/mai 2026 ARM</v>
       </c>
       <c r="O8" t="str">
-        <v>BENKHALIL Coralie</v>
+        <v>PASQUIER Delphine</v>
       </c>
       <c r="P8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q8">
         <v>19</v>
       </c>
       <c r="R8" s="1">
-        <v>38842</v>
+        <v>39143</v>
+      </c>
+      <c r="T8" t="str">
+        <v>Paris 20ème</v>
       </c>
       <c r="U8" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="V8" t="str">
-        <v>OUI</v>
+        <v>NON</v>
       </c>
       <c r="W8" t="str">
-        <v>22 Rue Curie</v>
+        <v>195B Rue du General Leclerc</v>
       </c>
       <c r="X8" t="str">
-        <v>59116</v>
+        <v>59280</v>
       </c>
       <c r="Y8" t="str">
-        <v>Houplines</v>
+        <v>Armentières</v>
       </c>
       <c r="Z8" t="str">
         <v>Non</v>
@@ -1648,7 +1672,7 @@
         <v>NON</v>
       </c>
       <c r="AD8" t="str">
-        <v>Infra 3</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE8" t="str">
         <v>Non</v>
@@ -1669,52 +1693,46 @@
         <v>Non</v>
       </c>
       <c r="AK8" t="str">
-        <v>102h30m</v>
+        <v>185h30m</v>
       </c>
       <c r="AL8" t="str">
-        <v>81h</v>
+        <v>84h</v>
       </c>
       <c r="AM8" t="str">
-        <v>34h15m</v>
+        <v>34h</v>
       </c>
       <c r="AN8" s="1">
-        <v>46125.37505787037</v>
+        <v>46160.39306712963</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>46202.66111111111</v>
       </c>
       <c r="AP8" s="1">
-        <v>46400.490277777775</v>
+        <v>46436.38402777778</v>
       </c>
       <c r="AU8" s="1">
-        <v>46049.8625</v>
+        <v>46126.342361111114</v>
       </c>
       <c r="AV8" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW8" t="str">
-        <v>DUTOIT Magali</v>
+        <v>En direct</v>
       </c>
       <c r="AX8" s="1">
-        <v>46048.86319444444</v>
-      </c>
-      <c r="AY8" t="str">
-        <v>mdutoit@aefavl.fr</v>
-      </c>
-      <c r="AZ8" t="str">
-        <v>0320109220</v>
+        <v>46119.384722222225</v>
       </c>
       <c r="BA8" t="str">
         <v>NON</v>
       </c>
       <c r="BG8" t="str">
-        <v>14472</v>
+        <v>17955</v>
       </c>
       <c r="BH8" s="1">
-        <v>45819.083333333336</v>
+        <v>45658.041666666664</v>
       </c>
       <c r="BI8" t="str">
-        <v>5912253M</v>
+        <v>5891142R</v>
       </c>
       <c r="BJ8" t="str">
-        <v>2385e5de-0257-4c75-8fe6-a73aba2bfc7b</v>
+        <v>a7a8a4fd-7f5c-466b-b700-3b4c088a10a1</v>
       </c>
       <c r="BK8" t="str">
         <v>Accepted</v>
@@ -1723,30 +1741,30 @@
         <v/>
       </c>
       <c r="BM8" t="str">
-        <v>duboishonny@gmail.com</v>
+        <v>gonzales_dominguez02@outlook.fr</v>
       </c>
       <c r="BN8" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/h_dubois_e2c-grandlille_fr/IgADLOKftMOeR5s0qC3DWrvmAV8L9ZUrDTGL2ZYyCB9yXW4?e=IP3Nbj</v>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/n_gonzalesdominguez_e2c-grandlille_fr/IgDMSy9vokCmS6gY4wtQwqCDAbnjA3f7iSA7Kf-aLxozU_Y?e=G5BdSh</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>78269</v>
+        <v>131806</v>
       </c>
       <c r="B9" t="str">
         <v>Femme</v>
       </c>
       <c r="C9" t="str">
-        <v>SIMON</v>
+        <v>CAPON</v>
       </c>
       <c r="D9" t="str">
-        <v>Emilie</v>
+        <v>Marie</v>
       </c>
       <c r="E9" t="str">
-        <v>e.simon@e2c-grandlille.fr</v>
+        <v>m.capon@e2c-grandlille.fr</v>
       </c>
       <c r="F9" t="str">
-        <v>07 67 05 44 37</v>
+        <v>06 38 15 01 68</v>
       </c>
       <c r="G9" t="str">
         <v>Grand Lille</v>
@@ -1754,44 +1772,44 @@
       <c r="H9" t="str">
         <v>Armentières</v>
       </c>
+      <c r="I9" t="str">
+        <v>Auxiliaire de vie sociale auprès d'enfants</v>
+      </c>
       <c r="K9" t="str">
         <v>J'explore</v>
       </c>
       <c r="L9" t="str">
-        <v>référés Jérôme</v>
+        <v>référés Delphine P.</v>
       </c>
       <c r="M9" t="str">
-        <v>2602/février 2026 ARM</v>
+        <v>2605/mai 2026 ARM</v>
       </c>
       <c r="O9" t="str">
-        <v>BOLPAIRE Jérôme</v>
+        <v>PASQUIER Delphine</v>
       </c>
       <c r="P9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R9" s="1">
-        <v>38982</v>
+        <v>39825</v>
       </c>
       <c r="T9" t="str">
-        <v>Beuvry</v>
+        <v>Cambrai</v>
       </c>
       <c r="U9" t="str">
         <v>FRANCAISE</v>
       </c>
-      <c r="V9" t="str">
-        <v>OUI</v>
-      </c>
       <c r="W9" t="str">
-        <v>1332 Rue du Touret</v>
+        <v>37 Rue de la Cite</v>
       </c>
       <c r="X9" t="str">
-        <v>62136</v>
+        <v>59280</v>
       </c>
       <c r="Y9" t="str">
-        <v>La Couture</v>
+        <v>Armentières</v>
       </c>
       <c r="Z9" t="str">
         <v>Non</v>
@@ -1803,7 +1821,7 @@
         <v>NON</v>
       </c>
       <c r="AD9" t="str">
-        <v>3 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE9" t="str">
         <v>Non</v>
@@ -1824,49 +1842,70 @@
         <v>Non</v>
       </c>
       <c r="AK9" t="str">
-        <v>298h30m</v>
+        <v>168h</v>
       </c>
       <c r="AL9" t="str">
-        <v>231h</v>
+        <v>103h10m</v>
       </c>
       <c r="AM9" t="str">
-        <v>25h45m</v>
+        <v>38h45m</v>
       </c>
       <c r="AN9" s="1">
-        <v>46055.653645833336</v>
+        <v>46160.38075231481</v>
       </c>
       <c r="AO9" s="1">
-        <v>46101.586805555555</v>
+        <v>46202.61388888889</v>
       </c>
       <c r="AP9" s="1">
-        <v>46328.36388888889</v>
+        <v>46436.43125</v>
       </c>
       <c r="AU9" s="1">
-        <v>45944.70763888889</v>
+        <v>46105.384722222225</v>
       </c>
       <c r="AV9" t="str">
-        <v>MISSION LOCALE DE L'ARTOIS - Antenne de LAVENTIE</v>
+        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
       </c>
       <c r="AW9" t="str">
-        <v>TAFFIN Jordan</v>
+        <v>Bouton Christelle</v>
       </c>
       <c r="AX9" s="1">
-        <v>45944.63958333333</v>
+        <v>46101.38611111111</v>
       </c>
       <c r="AY9" t="str">
-        <v>jordan.taffin@mlartois.org</v>
+        <v>cbouton@aefavl.fr</v>
       </c>
       <c r="AZ9" t="str">
-        <v>0321644940</v>
+        <v>0320109220</v>
       </c>
       <c r="BA9" t="str">
-        <v>NON</v>
+        <v>OUI</v>
+      </c>
+      <c r="BB9" t="str">
+        <v>CAPON</v>
+      </c>
+      <c r="BC9" t="str">
+        <v>Jean Michel et Cécile</v>
+      </c>
+      <c r="BD9" t="str">
+        <v>37 Rue de la Cité 59280 Armentières</v>
+      </c>
+      <c r="BE9" t="str">
+        <v>0671990029</v>
+      </c>
+      <c r="BF9" t="str">
+        <v>jean-michelcapon@sfr.fr</v>
       </c>
       <c r="BG9" t="str">
-        <v>10005</v>
+        <v>17724</v>
+      </c>
+      <c r="BH9" s="1">
+        <v>45993.041666666664</v>
+      </c>
+      <c r="BI9" t="str">
+        <v>5965657K</v>
       </c>
       <c r="BJ9" t="str">
-        <v>4426a9f4-481a-46f3-bd3e-bccf96a6d0f1</v>
+        <v>e194023d-d14a-44ef-a8f9-c3e7d69dce60</v>
       </c>
       <c r="BK9" t="str">
         <v>Accepted</v>
@@ -1875,30 +1914,30 @@
         <v/>
       </c>
       <c r="BM9" t="str">
-        <v>emiliesimon62136@gmail.com</v>
+        <v>mariecapon0@gmail.com</v>
       </c>
       <c r="BN9" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/m_capon_e2c-grandlille_fr/IgDaPA1uKQePRaPL1vaSt9BMAW9jK4Jly4rXPxebKuWo9lI?e=YW6VF3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>77845</v>
+        <v>78269</v>
       </c>
       <c r="B10" t="str">
         <v>Femme</v>
       </c>
       <c r="C10" t="str">
-        <v>BOURGEOIS--BILAU</v>
+        <v>SIMON</v>
       </c>
       <c r="D10" t="str">
-        <v>Ciara</v>
+        <v>Emilie</v>
       </c>
       <c r="E10" t="str">
-        <v>c.bourgeoisbilau@e2c-grandlille.fr</v>
+        <v>e.simon@e2c-grandlille.fr</v>
       </c>
       <c r="F10" t="str">
-        <v>07 49 52 21 24</v>
+        <v>07 67 05 44 37</v>
       </c>
       <c r="G10" t="str">
         <v>Grand Lille</v>
@@ -1906,32 +1945,29 @@
       <c r="H10" t="str">
         <v>Armentières</v>
       </c>
-      <c r="I10" t="str">
-        <v>Esthéticien / Esthéticienne</v>
-      </c>
       <c r="K10" t="str">
-        <v>J'ai des idées</v>
+        <v>J'explore</v>
       </c>
       <c r="L10" t="str">
-        <v>référés Gérard</v>
+        <v>référés Jérôme</v>
       </c>
       <c r="M10" t="str">
-        <v>2604/avril 2026 ARM</v>
+        <v>2602/février 2026 ARM</v>
       </c>
       <c r="O10" t="str">
-        <v>NOWINSKI Gérard</v>
+        <v>BOLPAIRE Jérôme</v>
       </c>
       <c r="P10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R10" s="1">
-        <v>40163</v>
+        <v>38982</v>
       </c>
       <c r="T10" t="str">
-        <v>Lille</v>
+        <v>Beuvry</v>
       </c>
       <c r="U10" t="str">
         <v>FRANCAISE</v>
@@ -1940,13 +1976,13 @@
         <v>OUI</v>
       </c>
       <c r="W10" t="str">
-        <v>7 Cite des Fermes</v>
+        <v>1332 Rue du Touret</v>
       </c>
       <c r="X10" t="str">
-        <v>59930</v>
+        <v>62136</v>
       </c>
       <c r="Y10" t="str">
-        <v>La Chapelle-d'Armentières</v>
+        <v>La Couture</v>
       </c>
       <c r="Z10" t="str">
         <v>Non</v>
@@ -1958,7 +1994,7 @@
         <v>NON</v>
       </c>
       <c r="AD10" t="str">
-        <v>3 non validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE10" t="str">
         <v>Non</v>
@@ -1979,67 +2015,49 @@
         <v>Non</v>
       </c>
       <c r="AK10" t="str">
-        <v>113h30m</v>
+        <v>422h30m</v>
       </c>
       <c r="AL10" t="str">
-        <v>28h</v>
+        <v>301h</v>
       </c>
       <c r="AM10" t="str">
-        <v>19h30m</v>
+        <v>41h45m</v>
       </c>
       <c r="AN10" s="1">
-        <v>46125.373611111114</v>
+        <v>46055.653645833336</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>46101.586805555555</v>
       </c>
       <c r="AP10" s="1">
-        <v>46400.68402777778</v>
+        <v>46328.36388888889</v>
       </c>
       <c r="AU10" s="1">
-        <v>46049.501388888886</v>
+        <v>45944.70763888889</v>
       </c>
       <c r="AV10" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
+        <v>MISSION LOCALE DE L'ARTOIS - Antenne de LAVENTIE</v>
       </c>
       <c r="AW10" t="str">
-        <v>DERYCKERE Antoine</v>
+        <v>TAFFIN Jordan</v>
       </c>
       <c r="AX10" s="1">
-        <v>46043.50277777778</v>
+        <v>45944.63958333333</v>
       </c>
       <c r="AY10" t="str">
-        <v>aderyckere@aefavl.fr</v>
+        <v>jordan.taffin@mlartois.org</v>
       </c>
       <c r="AZ10" t="str">
-        <v>03210109220</v>
+        <v>0321644940</v>
       </c>
       <c r="BA10" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB10" t="str">
-        <v>Bourgeois</v>
-      </c>
-      <c r="BC10" t="str">
-        <v>Anthony</v>
-      </c>
-      <c r="BD10" t="str">
-        <v>7 Cité des Fermes 59930 La Chapelle d'Armentières</v>
-      </c>
-      <c r="BE10" t="str">
-        <v>0783452234</v>
-      </c>
-      <c r="BF10" t="str">
-        <v>tony19792010@hotmail.fr</v>
+        <v>NON</v>
       </c>
       <c r="BG10" t="str">
-        <v>14454</v>
-      </c>
-      <c r="BH10" s="1">
-        <v>46009.041666666664</v>
-      </c>
-      <c r="BI10" t="str">
-        <v>5969356F</v>
+        <v>10005</v>
       </c>
       <c r="BJ10" t="str">
-        <v>55e946e7-5e02-41b9-92c8-4df8048650e7</v>
+        <v>4426a9f4-481a-46f3-bd3e-bccf96a6d0f1</v>
       </c>
       <c r="BK10" t="str">
         <v>Accepted</v>
@@ -2048,10 +2066,10 @@
         <v/>
       </c>
       <c r="BM10" t="str">
-        <v>tony19792010@hotmail.fr</v>
+        <v>emiliesimon62136@gmail.com</v>
       </c>
       <c r="BN10" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/c_bourgeoisbilau_e2c-grandlille_fr/IgAxls9dq3WaSbwPq8KEbbGDAfItxp63MPeA4ZPmN_vohFA?e=Fhhz60</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2103,6 +2121,9 @@
       <c r="R11" s="1">
         <v>38755</v>
       </c>
+      <c r="T11" t="str">
+        <v>Armentières</v>
+      </c>
       <c r="U11" t="str">
         <v>FRANCAISE</v>
       </c>
@@ -2149,16 +2170,19 @@
         <v>Non</v>
       </c>
       <c r="AK11" t="str">
-        <v>93h30m</v>
+        <v>239h</v>
       </c>
       <c r="AL11" t="str">
-        <v>97h</v>
+        <v>191h</v>
       </c>
       <c r="AM11" t="str">
-        <v>21h</v>
+        <v>23h45m</v>
       </c>
       <c r="AN11" s="1">
         <v>46125.38060185185</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>46181.41166666667</v>
       </c>
       <c r="AP11" s="1">
         <v>46400.65069444444</v>
@@ -2292,7 +2316,7 @@
         <v>Non</v>
       </c>
       <c r="AG12" t="str">
-        <v>EN_COURS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH12" t="str">
         <v>Non</v>
@@ -2304,16 +2328,19 @@
         <v>Non</v>
       </c>
       <c r="AK12" t="str">
-        <v>130h45m</v>
+        <v>245h</v>
       </c>
       <c r="AL12" t="str">
-        <v>60h</v>
+        <v>155h</v>
       </c>
       <c r="AM12" t="str">
-        <v>16h15m</v>
+        <v>32h30m</v>
       </c>
       <c r="AN12" s="1">
         <v>46125.36341435185</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>46178.35763888889</v>
       </c>
       <c r="AP12" s="1">
         <v>46400.674305555556</v>
@@ -2477,13 +2504,13 @@
         <v>Non</v>
       </c>
       <c r="AK13" t="str">
-        <v>131h</v>
+        <v>258h</v>
       </c>
       <c r="AL13" t="str">
-        <v>90h</v>
+        <v>194h</v>
       </c>
       <c r="AM13" t="str">
-        <v>3h15m</v>
+        <v>13h</v>
       </c>
       <c r="AN13" s="1">
         <v>46125.36083333333</v>
@@ -2638,13 +2665,13 @@
         <v>Non</v>
       </c>
       <c r="AK14" t="str">
-        <v>207h30m</v>
+        <v>330h30m</v>
       </c>
       <c r="AL14" t="str">
-        <v>168h</v>
+        <v>273h</v>
       </c>
       <c r="AM14" t="str">
-        <v>18h</v>
+        <v>31h</v>
       </c>
       <c r="AN14" s="1">
         <v>46090.37569444445</v>
@@ -2796,13 +2823,13 @@
         <v>Non</v>
       </c>
       <c r="AK15" t="str">
-        <v>121h15m</v>
+        <v>222h45m</v>
       </c>
       <c r="AL15" t="str">
-        <v>105h</v>
+        <v>183h</v>
       </c>
       <c r="AM15" t="str">
-        <v>13h</v>
+        <v>49h</v>
       </c>
       <c r="AN15" s="1">
         <v>46125.37805555556</v>
@@ -2933,7 +2960,7 @@
         <v>NON</v>
       </c>
       <c r="AD16" t="str">
-        <v>[OLD]Niveau 4 validé</v>
+        <v>4 non validé</v>
       </c>
       <c r="AE16" t="str">
         <v>Non</v>
@@ -2954,13 +2981,13 @@
         <v>Non</v>
       </c>
       <c r="AK16" t="str">
-        <v>291h</v>
+        <v>403h</v>
       </c>
       <c r="AL16" t="str">
-        <v>198h30m</v>
+        <v>296h30m</v>
       </c>
       <c r="AM16" t="str">
-        <v>42h</v>
+        <v>61h30m</v>
       </c>
       <c r="AN16" s="1">
         <v>46055.648564814815</v>
@@ -3115,16 +3142,19 @@
         <v>Non</v>
       </c>
       <c r="AK17" t="str">
-        <v>216h15m</v>
+        <v>306h15m</v>
       </c>
       <c r="AL17" t="str">
-        <v>162h</v>
+        <v>256h15m</v>
       </c>
       <c r="AM17" t="str">
-        <v>17h45m</v>
+        <v>61h45m</v>
       </c>
       <c r="AN17" s="1">
         <v>46090.37708333333</v>
+      </c>
+      <c r="AO17" s="1">
+        <v>46139.60208333333</v>
       </c>
       <c r="AP17" s="1">
         <v>46365.580555555556</v>
@@ -3177,22 +3207,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>57645</v>
+        <v>57591</v>
       </c>
       <c r="B18" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C18" t="str">
-        <v>SCHIAVONI</v>
+        <v>SACKO</v>
       </c>
       <c r="D18" t="str">
-        <v>Sam</v>
+        <v>Dieynaba</v>
       </c>
       <c r="E18" t="str">
-        <v>s.schiavoni@e2c-grandlille.fr</v>
+        <v>d.sacko@e2c-grandlille.fr</v>
       </c>
       <c r="F18" t="str">
-        <v>0781717162</v>
+        <v>07 45 33 95 47</v>
       </c>
       <c r="G18" t="str">
         <v>Grand Lille</v>
@@ -3201,31 +3231,31 @@
         <v>Armentières</v>
       </c>
       <c r="I18" t="str">
-        <v>Jardinier / Jardinière d'espaces verts</v>
+        <v>Agent administratif / Agente administrative</v>
       </c>
       <c r="K18" t="str">
-        <v>J'explore</v>
+        <v>Je sais</v>
       </c>
       <c r="L18" t="str">
         <v>référés Gérard</v>
       </c>
       <c r="M18" t="str">
-        <v>2603/mars 2026 ARM</v>
+        <v>2602/février 2026 ARM</v>
       </c>
       <c r="O18" t="str">
         <v>NOWINSKI Gérard</v>
       </c>
       <c r="P18">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q18">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R18" s="1">
-        <v>39113</v>
+        <v>38056</v>
       </c>
       <c r="T18" t="str">
-        <v>Armentières, FRANCE</v>
+        <v>Creil, FRANCE</v>
       </c>
       <c r="U18" t="str">
         <v>FRANCAISE</v>
@@ -3234,7 +3264,7 @@
         <v>OUI</v>
       </c>
       <c r="W18" t="str">
-        <v>16 16 Rue Des Patineurs</v>
+        <v>7 P 7 Place du 19 Mars 1962</v>
       </c>
       <c r="X18" t="str">
         <v>59280</v>
@@ -3243,7 +3273,10 @@
         <v>ARMENTIERES</v>
       </c>
       <c r="Z18" t="str">
-        <v>Non</v>
+        <v>Oui</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>QN05967M</v>
       </c>
       <c r="AB18" t="str">
         <v>Non</v>
@@ -3273,55 +3306,55 @@
         <v>Non</v>
       </c>
       <c r="AK18" t="str">
-        <v>196h15m</v>
+        <v>254h15m</v>
       </c>
       <c r="AL18" t="str">
-        <v>105h</v>
+        <v>357h</v>
       </c>
       <c r="AM18" t="str">
-        <v>37h30m</v>
+        <v>156h30m</v>
       </c>
       <c r="AN18" s="1">
-        <v>46090.376388888886</v>
+        <v>46055.652337962965</v>
       </c>
       <c r="AO18" s="1">
-        <v>46136.34027777778</v>
+        <v>46104.614583333336</v>
       </c>
       <c r="AP18" s="1">
-        <v>46365.57777777778</v>
+        <v>46328.615277777775</v>
       </c>
       <c r="AU18" s="1">
-        <v>45979</v>
+        <v>45932</v>
       </c>
       <c r="AV18" t="str">
-        <v>FRANCE TRAVAIL -Armentières-</v>
+        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
       </c>
       <c r="AW18" t="str">
-        <v>Nathalie DELAHAYE</v>
+        <v>Christelle BOUTON</v>
       </c>
       <c r="AX18" s="1">
-        <v>45979</v>
+        <v>45929</v>
       </c>
       <c r="AY18" t="str">
-        <v>nathalie.delahaye01@francetravail.fr</v>
+        <v>cbouton@aefavl.fr</v>
       </c>
       <c r="AZ18" t="str">
-        <v>0320778686</v>
+        <v>0320109220</v>
       </c>
       <c r="BA18" t="str">
         <v>NON</v>
       </c>
       <c r="BG18" t="str">
-        <v>11390</v>
+        <v>10152</v>
       </c>
       <c r="BH18" s="1">
-        <v>45929.083333333336</v>
+        <v>45835.083333333336</v>
       </c>
       <c r="BI18" t="str">
-        <v>5946431M</v>
+        <v>5874121P</v>
       </c>
       <c r="BJ18" t="str">
-        <v>b24072fe-ee9e-4606-b736-86a7a87f913a</v>
+        <v>1234f51f-d852-4bfe-bae9-61f1f02502cc</v>
       </c>
       <c r="BK18" t="str">
         <v>Accepted</v>
@@ -3330,30 +3363,30 @@
         <v/>
       </c>
       <c r="BM18" t="str">
-        <v>schiavonisam@gmail.com</v>
+        <v>sackodieynaba9@gmail.com</v>
       </c>
       <c r="BN18" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/s_schiavoni_e2c-grandlille_fr/IgCj9rm83k58SrhH1AryUpvxATW1MyFSjQ0e-O98soPvRTE?e=hsoKTN</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>57591</v>
+        <v>57124</v>
       </c>
       <c r="B19" t="str">
         <v>Femme</v>
       </c>
       <c r="C19" t="str">
-        <v>SACKO</v>
+        <v>MALESYS</v>
       </c>
       <c r="D19" t="str">
-        <v>Dieynaba</v>
+        <v>Solène</v>
       </c>
       <c r="E19" t="str">
-        <v>d.sacko@e2c-grandlille.fr</v>
+        <v>s.malesys@e2c-grandlille.fr</v>
       </c>
       <c r="F19" t="str">
-        <v>07 45 33 95 47</v>
+        <v>06 77 11 30 63</v>
       </c>
       <c r="G19" t="str">
         <v>Grand Lille</v>
@@ -3362,31 +3395,31 @@
         <v>Armentières</v>
       </c>
       <c r="I19" t="str">
-        <v>Agent administratif / Agente administrative</v>
+        <v>Préparateur / Préparatrice de véhicules automobiles</v>
       </c>
       <c r="K19" t="str">
         <v>Je sais</v>
       </c>
       <c r="L19" t="str">
-        <v>référés Gérard</v>
+        <v>référés Jérôme</v>
       </c>
       <c r="M19" t="str">
         <v>2602/février 2026 ARM</v>
       </c>
       <c r="O19" t="str">
-        <v>NOWINSKI Gérard</v>
+        <v>BOLPAIRE Jérôme</v>
       </c>
       <c r="P19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q19">
         <v>21</v>
       </c>
       <c r="R19" s="1">
-        <v>38056</v>
+        <v>38204</v>
       </c>
       <c r="T19" t="str">
-        <v>Creil, FRANCE</v>
+        <v>Lille, FRANCE</v>
       </c>
       <c r="U19" t="str">
         <v>FRANCAISE</v>
@@ -3395,19 +3428,16 @@
         <v>OUI</v>
       </c>
       <c r="W19" t="str">
-        <v>7 P 7 Place du 19 Mars 1962</v>
+        <v>17 17 Résidence La Guennerie</v>
       </c>
       <c r="X19" t="str">
-        <v>59280</v>
+        <v>62840</v>
       </c>
       <c r="Y19" t="str">
-        <v>ARMENTIERES</v>
+        <v>LAVENTIE</v>
       </c>
       <c r="Z19" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AA19" t="str">
-        <v>QN05967M</v>
+        <v>Non</v>
       </c>
       <c r="AB19" t="str">
         <v>Non</v>
@@ -3416,7 +3446,7 @@
         <v>NON</v>
       </c>
       <c r="AD19" t="str">
-        <v>4 validé</v>
+        <v>3 non validé</v>
       </c>
       <c r="AE19" t="str">
         <v>Non</v>
@@ -3437,55 +3467,49 @@
         <v>Non</v>
       </c>
       <c r="AK19" t="str">
-        <v>191h45m</v>
+        <v>416h</v>
       </c>
       <c r="AL19" t="str">
-        <v>287h</v>
+        <v>317h30m</v>
       </c>
       <c r="AM19" t="str">
-        <v>80h45m</v>
+        <v>35h45m</v>
       </c>
       <c r="AN19" s="1">
-        <v>46055.652337962965</v>
+        <v>46055.652592592596</v>
       </c>
       <c r="AO19" s="1">
-        <v>46104.614583333336</v>
+        <v>46104.62322916667</v>
       </c>
       <c r="AP19" s="1">
-        <v>46328.615277777775</v>
+        <v>46328.62291666667</v>
       </c>
       <c r="AU19" s="1">
-        <v>45932</v>
+        <v>45979</v>
       </c>
       <c r="AV19" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
+        <v>Mission Locale de l'Artois - Antenne de Béthune</v>
       </c>
       <c r="AW19" t="str">
-        <v>Christelle BOUTON</v>
+        <v>Jordan TAFFIN</v>
       </c>
       <c r="AX19" s="1">
-        <v>45929</v>
+        <v>45979</v>
       </c>
       <c r="AY19" t="str">
-        <v>cbouton@aefavl.fr</v>
+        <v>jordan.taffin@mlartois.org</v>
       </c>
       <c r="AZ19" t="str">
-        <v>0320109220</v>
+        <v>0321644940</v>
       </c>
       <c r="BA19" t="str">
         <v>NON</v>
       </c>
       <c r="BG19" t="str">
-        <v>10152</v>
-      </c>
-      <c r="BH19" s="1">
-        <v>45835.083333333336</v>
-      </c>
-      <c r="BI19" t="str">
-        <v>5874121P</v>
+        <v>10003</v>
       </c>
       <c r="BJ19" t="str">
-        <v>1234f51f-d852-4bfe-bae9-61f1f02502cc</v>
+        <v>915d62cc-29b2-49b5-ad2e-9a013e67847a</v>
       </c>
       <c r="BK19" t="str">
         <v>Accepted</v>
@@ -3494,7 +3518,7 @@
         <v/>
       </c>
       <c r="BM19" t="str">
-        <v/>
+        <v>malesys.solene5@gmail.com</v>
       </c>
       <c r="BN19" t="str">
         <v/>
@@ -3502,22 +3526,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>57124</v>
+        <v>56284</v>
       </c>
       <c r="B20" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C20" t="str">
-        <v>MALESYS</v>
+        <v>DUBOIS</v>
       </c>
       <c r="D20" t="str">
-        <v>Solène</v>
+        <v>Lorenzo</v>
       </c>
       <c r="E20" t="str">
-        <v>s.malesys@e2c-grandlille.fr</v>
+        <v>l.dubois@e2c-grandlille.fr</v>
       </c>
       <c r="F20" t="str">
-        <v>06 77 11 30 63</v>
+        <v>06 26 22 69 21</v>
       </c>
       <c r="G20" t="str">
         <v>Grand Lille</v>
@@ -3526,31 +3550,31 @@
         <v>Armentières</v>
       </c>
       <c r="I20" t="str">
-        <v>Préparateur / Préparatrice de véhicules automobiles</v>
+        <v>Mécanicien / Mécanicienne automobile</v>
       </c>
       <c r="K20" t="str">
         <v>Je sais</v>
       </c>
       <c r="L20" t="str">
-        <v>référés Jérôme</v>
+        <v>référés Coralie</v>
       </c>
       <c r="M20" t="str">
         <v>2602/février 2026 ARM</v>
       </c>
       <c r="O20" t="str">
-        <v>BOLPAIRE Jérôme</v>
+        <v>BENKHALIL Coralie</v>
       </c>
       <c r="P20">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q20">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R20" s="1">
-        <v>38204</v>
+        <v>39639</v>
       </c>
       <c r="T20" t="str">
-        <v>Lille, FRANCE</v>
+        <v>Armentières, FRANCE</v>
       </c>
       <c r="U20" t="str">
         <v>FRANCAISE</v>
@@ -3559,13 +3583,13 @@
         <v>OUI</v>
       </c>
       <c r="W20" t="str">
-        <v>17 17 Résidence La Guennerie</v>
+        <v>1 Allée Martha Desrumaux</v>
       </c>
       <c r="X20" t="str">
-        <v>62840</v>
+        <v>59116</v>
       </c>
       <c r="Y20" t="str">
-        <v>LAVENTIE</v>
+        <v>Houplines</v>
       </c>
       <c r="Z20" t="str">
         <v>Non</v>
@@ -3577,7 +3601,7 @@
         <v>NON</v>
       </c>
       <c r="AD20" t="str">
-        <v>3 non validé</v>
+        <v>Infra 3</v>
       </c>
       <c r="AE20" t="str">
         <v>Non</v>
@@ -3598,49 +3622,49 @@
         <v>Non</v>
       </c>
       <c r="AK20" t="str">
-        <v>303h15m</v>
+        <v>352h45m</v>
       </c>
       <c r="AL20" t="str">
-        <v>233h30m</v>
+        <v>225h</v>
       </c>
       <c r="AM20" t="str">
-        <v>27h30m</v>
+        <v>124h30m</v>
       </c>
       <c r="AN20" s="1">
-        <v>46055.652592592596</v>
+        <v>46055.65342592593</v>
       </c>
       <c r="AO20" s="1">
-        <v>46104.62322916667</v>
+        <v>46101.61736111111</v>
       </c>
       <c r="AP20" s="1">
-        <v>46328.62291666667</v>
+        <v>46328.57152777778</v>
       </c>
       <c r="AU20" s="1">
-        <v>45979</v>
+        <v>45932</v>
       </c>
       <c r="AV20" t="str">
-        <v>Mission Locale de l'Artois - Antenne de Béthune</v>
+        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
       </c>
       <c r="AW20" t="str">
-        <v>Jordan TAFFIN</v>
+        <v>Antoine DERYCKERE</v>
       </c>
       <c r="AX20" s="1">
-        <v>45979</v>
+        <v>45915</v>
       </c>
       <c r="AY20" t="str">
-        <v>jordan.taffin@mlartois.org</v>
+        <v>aderyckere@aefavl.fr</v>
       </c>
       <c r="AZ20" t="str">
-        <v>0321644940</v>
+        <v>0320109220</v>
       </c>
       <c r="BA20" t="str">
         <v>NON</v>
       </c>
       <c r="BG20" t="str">
-        <v>10003</v>
+        <v>10174</v>
       </c>
       <c r="BJ20" t="str">
-        <v>915d62cc-29b2-49b5-ad2e-9a013e67847a</v>
+        <v>bc30a909-c87c-4266-9da2-724f9adce51c</v>
       </c>
       <c r="BK20" t="str">
         <v>Accepted</v>
@@ -3649,7 +3673,7 @@
         <v/>
       </c>
       <c r="BM20" t="str">
-        <v>malesys.solene5@gmail.com</v>
+        <v>lorenzodubois2008@gmail.com</v>
       </c>
       <c r="BN20" t="str">
         <v/>
@@ -3657,22 +3681,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>56284</v>
+        <v>56228</v>
       </c>
       <c r="B21" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C21" t="str">
-        <v>DUBOIS</v>
+        <v>DIALLO</v>
       </c>
       <c r="D21" t="str">
-        <v>Lorenzo</v>
+        <v>Houssainatou</v>
       </c>
       <c r="E21" t="str">
-        <v>l.dubois@e2c-grandlille.fr</v>
+        <v>h.diallo@e2c-grandlille.fr</v>
       </c>
       <c r="F21" t="str">
-        <v>06 26 22 69 21</v>
+        <v>06 51 86 58 19</v>
       </c>
       <c r="G21" t="str">
         <v>Grand Lille</v>
@@ -3681,46 +3705,46 @@
         <v>Armentières</v>
       </c>
       <c r="I21" t="str">
-        <v>Mécanicien / Mécanicienne automobile</v>
+        <v>Aide-soignant / Aide-soignante</v>
       </c>
       <c r="K21" t="str">
-        <v>Je sais</v>
+        <v>J'ai des idées</v>
       </c>
       <c r="L21" t="str">
-        <v>référés Coralie</v>
+        <v>référés Gérard</v>
       </c>
       <c r="M21" t="str">
-        <v>2602/février 2026 ARM</v>
+        <v>2603/mars 2026 ARM</v>
       </c>
       <c r="O21" t="str">
-        <v>BENKHALIL Coralie</v>
+        <v>NOWINSKI Gérard</v>
       </c>
       <c r="P21">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q21">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R21" s="1">
-        <v>39639</v>
+        <v>38329</v>
       </c>
       <c r="T21" t="str">
-        <v>Armentières, FRANCE</v>
+        <v>Guinée, GUINÉE</v>
       </c>
       <c r="U21" t="str">
-        <v>FRANCAISE</v>
+        <v>AUTRE</v>
       </c>
       <c r="V21" t="str">
         <v>OUI</v>
       </c>
       <c r="W21" t="str">
-        <v>1 Allée Martha Desrumaux</v>
+        <v>5 Rue Bayart</v>
       </c>
       <c r="X21" t="str">
-        <v>59116</v>
+        <v>59280</v>
       </c>
       <c r="Y21" t="str">
-        <v>Houplines</v>
+        <v>Armentières</v>
       </c>
       <c r="Z21" t="str">
         <v>Non</v>
@@ -3732,7 +3756,7 @@
         <v>NON</v>
       </c>
       <c r="AD21" t="str">
-        <v>Infra 3</v>
+        <v>4 validé</v>
       </c>
       <c r="AE21" t="str">
         <v>Non</v>
@@ -3753,37 +3777,37 @@
         <v>Non</v>
       </c>
       <c r="AK21" t="str">
-        <v>270h30m</v>
+        <v>261h15m</v>
       </c>
       <c r="AL21" t="str">
-        <v>133h</v>
+        <v>350h</v>
       </c>
       <c r="AM21" t="str">
-        <v>73h</v>
+        <v>22h30m</v>
       </c>
       <c r="AN21" s="1">
-        <v>46055.65342592593</v>
+        <v>46090.375</v>
       </c>
       <c r="AO21" s="1">
-        <v>46101.61736111111</v>
+        <v>46202.65625</v>
       </c>
       <c r="AP21" s="1">
-        <v>46328.57152777778</v>
+        <v>46365.55763888889</v>
       </c>
       <c r="AU21" s="1">
-        <v>45932</v>
+        <v>45937</v>
       </c>
       <c r="AV21" t="str">
         <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
       </c>
       <c r="AW21" t="str">
-        <v>Antoine DERYCKERE</v>
+        <v>Salim ZEGAOUI</v>
       </c>
       <c r="AX21" s="1">
-        <v>45915</v>
+        <v>45937</v>
       </c>
       <c r="AY21" t="str">
-        <v>aderyckere@aefavl.fr</v>
+        <v>szegaoui@aefavl.fr</v>
       </c>
       <c r="AZ21" t="str">
         <v>0320109220</v>
@@ -3792,10 +3816,16 @@
         <v>NON</v>
       </c>
       <c r="BG21" t="str">
-        <v>10174</v>
+        <v>11325</v>
+      </c>
+      <c r="BH21" s="1">
+        <v>46045.041666666664</v>
+      </c>
+      <c r="BI21" t="str">
+        <v>5976870Y</v>
       </c>
       <c r="BJ21" t="str">
-        <v>bc30a909-c87c-4266-9da2-724f9adce51c</v>
+        <v>e10ac9a1-e00d-4cb9-8197-55b3896041a0</v>
       </c>
       <c r="BK21" t="str">
         <v>Accepted</v>
@@ -3804,30 +3834,30 @@
         <v/>
       </c>
       <c r="BM21" t="str">
-        <v>lorenzodubois2008@gmail.com</v>
+        <v>dialloapha23ousmane@gmail.com</v>
       </c>
       <c r="BN21" t="str">
-        <v/>
+        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/h_diallo_e2c-grandlille_fr/IgDfKMz6b59FSoMky7W89n8gARd8I5RTIsGqMKynEvGOBO8?e=WgJpjO</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>56228</v>
+        <v>39964</v>
       </c>
       <c r="B22" t="str">
-        <v>Femme</v>
+        <v>Homme</v>
       </c>
       <c r="C22" t="str">
-        <v>DIALLO</v>
+        <v>BAUDELET</v>
       </c>
       <c r="D22" t="str">
-        <v>Houssainatou</v>
+        <v>Vivien</v>
       </c>
       <c r="E22" t="str">
-        <v>h.diallo@e2c-grandlille.fr</v>
+        <v>vivien.baudelet59840@gmail.com</v>
       </c>
       <c r="F22" t="str">
-        <v>06 51 86 58 19</v>
+        <v>0610533593</v>
       </c>
       <c r="G22" t="str">
         <v>Grand Lille</v>
@@ -3836,46 +3866,43 @@
         <v>Armentières</v>
       </c>
       <c r="I22" t="str">
-        <v>Aide-soignant / Aide-soignante</v>
+        <v>Commis de cuisine tournant / Commise de cuisine tournante</v>
       </c>
       <c r="K22" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L22" t="str">
-        <v>référés Gérard</v>
+        <v>référés Coralie</v>
       </c>
       <c r="M22" t="str">
-        <v>2603/mars 2026 ARM</v>
+        <v>2512/décembre 2025 ARM</v>
       </c>
       <c r="O22" t="str">
-        <v>NOWINSKI Gérard</v>
+        <v>BENKHALIL Coralie</v>
       </c>
       <c r="P22">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q22">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R22" s="1">
-        <v>38329</v>
+        <v>37252</v>
       </c>
       <c r="T22" t="str">
-        <v>Guinée, GUINÉE</v>
+        <v>Amiens</v>
       </c>
       <c r="U22" t="str">
-        <v>AUTRE</v>
-      </c>
-      <c r="V22" t="str">
-        <v>OUI</v>
+        <v>FRANCAISE</v>
       </c>
       <c r="W22" t="str">
-        <v>5 Rue Bayart</v>
+        <v>37 37 Rue Victor Hugo Bât 304B</v>
       </c>
       <c r="X22" t="str">
-        <v>59280</v>
+        <v>59116</v>
       </c>
       <c r="Y22" t="str">
-        <v>Armentières</v>
+        <v>HOUPLINES</v>
       </c>
       <c r="Z22" t="str">
         <v>Non</v>
@@ -3887,7 +3914,7 @@
         <v>NON</v>
       </c>
       <c r="AD22" t="str">
-        <v>4 validé</v>
+        <v>3 validé</v>
       </c>
       <c r="AE22" t="str">
         <v>Non</v>
@@ -3899,7 +3926,7 @@
         <v>SANS</v>
       </c>
       <c r="AH22" t="str">
-        <v>Non</v>
+        <v>Oui</v>
       </c>
       <c r="AI22" t="str">
         <v>Non</v>
@@ -3908,52 +3935,34 @@
         <v>Non</v>
       </c>
       <c r="AK22" t="str">
-        <v>185h15m</v>
+        <v>471h</v>
       </c>
       <c r="AL22" t="str">
-        <v>196h</v>
+        <v>396h30m</v>
       </c>
       <c r="AM22" t="str">
-        <v>14h30m</v>
+        <v>61h15m</v>
       </c>
       <c r="AN22" s="1">
-        <v>46090.375</v>
+        <v>46006</v>
+      </c>
+      <c r="AO22" s="1">
+        <v>46066.40833333333</v>
       </c>
       <c r="AP22" s="1">
-        <v>46365.55763888889</v>
-      </c>
-      <c r="AU22" s="1">
-        <v>45937</v>
+        <v>46280.083333333336</v>
       </c>
       <c r="AV22" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW22" t="str">
-        <v>Salim ZEGAOUI</v>
-      </c>
-      <c r="AX22" s="1">
-        <v>45937</v>
-      </c>
-      <c r="AY22" t="str">
-        <v>szegaoui@aefavl.fr</v>
-      </c>
-      <c r="AZ22" t="str">
-        <v>0320109220</v>
+        <v>En direct</v>
       </c>
       <c r="BA22" t="str">
         <v>NON</v>
       </c>
       <c r="BG22" t="str">
-        <v>11325</v>
-      </c>
-      <c r="BH22" s="1">
-        <v>46045.041666666664</v>
-      </c>
-      <c r="BI22" t="str">
-        <v>5976870Y</v>
+        <v>598052</v>
       </c>
       <c r="BJ22" t="str">
-        <v>e10ac9a1-e00d-4cb9-8197-55b3896041a0</v>
+        <v>78db74bf-aef8-401d-a236-6b0643e4fde4</v>
       </c>
       <c r="BK22" t="str">
         <v>Accepted</v>
@@ -3962,30 +3971,30 @@
         <v/>
       </c>
       <c r="BM22" t="str">
-        <v>dialloapha23ousmane@gmail.com</v>
+        <v/>
       </c>
       <c r="BN22" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/h_diallo_e2c-grandlille_fr/IgDfKMz6b59FSoMky7W89n8gARd8I5RTIsGqMKynEvGOBO8?e=WgJpjO</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>56128</v>
+        <v>36687</v>
       </c>
       <c r="B23" t="str">
-        <v>Homme</v>
+        <v>Femme</v>
       </c>
       <c r="C23" t="str">
-        <v>DERENONCOURT</v>
+        <v>LANDAS</v>
       </c>
       <c r="D23" t="str">
-        <v>Ethann</v>
+        <v>Kimberley</v>
       </c>
       <c r="E23" t="str">
-        <v>e.derenoncourt@e2c-grandlille.fr</v>
+        <v>landas.kimberley@gmail.com</v>
       </c>
       <c r="F23" t="str">
-        <v>0631710555</v>
+        <v>0614742515</v>
       </c>
       <c r="G23" t="str">
         <v>Grand Lille</v>
@@ -3994,40 +4003,40 @@
         <v>Armentières</v>
       </c>
       <c r="I23" t="str">
-        <v>Assistant / Assistante logistique</v>
+        <v>Assistant / Assistante accueil petite enfance</v>
       </c>
       <c r="K23" t="str">
-        <v>J'ai des idées</v>
+        <v>Je sais</v>
       </c>
       <c r="L23" t="str">
-        <v>référés Coralie</v>
+        <v>référés Delphine P.</v>
       </c>
       <c r="M23" t="str">
-        <v>2603/mars 2026 ARM</v>
+        <v>2511/novembre 2025 ARM</v>
       </c>
       <c r="O23" t="str">
-        <v>BENKHALIL Coralie</v>
+        <v>PASQUIER Delphine</v>
       </c>
       <c r="P23">
+        <v>18</v>
+      </c>
+      <c r="Q23">
         <v>17</v>
       </c>
-      <c r="Q23">
-        <v>16</v>
-      </c>
       <c r="R23" s="1">
-        <v>39959</v>
+        <v>39401</v>
       </c>
       <c r="T23" t="str">
-        <v>FRANCE</v>
+        <v>Armentières</v>
       </c>
       <c r="U23" t="str">
         <v>FRANCAISE</v>
       </c>
       <c r="V23" t="str">
-        <v>OUI</v>
+        <v>NON</v>
       </c>
       <c r="W23" t="str">
-        <v>12 12 Rue Des Murets</v>
+        <v>23 23 Rue Félix Faure</v>
       </c>
       <c r="X23" t="str">
         <v>59280</v>
@@ -4045,7 +4054,7 @@
         <v>NON</v>
       </c>
       <c r="AD23" t="str">
-        <v>Infra 3</v>
+        <v>3 validé</v>
       </c>
       <c r="AE23" t="str">
         <v>Non</v>
@@ -4054,7 +4063,7 @@
         <v>Non</v>
       </c>
       <c r="AG23" t="str">
-        <v>SANS</v>
+        <v>AVEC</v>
       </c>
       <c r="AH23" t="str">
         <v>Non</v>
@@ -4066,70 +4075,37 @@
         <v>Non</v>
       </c>
       <c r="AK23" t="str">
-        <v>159h45m</v>
+        <v>583h30m</v>
       </c>
       <c r="AL23" t="str">
-        <v>177h45m</v>
+        <v>319h45m</v>
       </c>
       <c r="AM23" t="str">
-        <v>74h15m</v>
+        <v>106h45m</v>
       </c>
       <c r="AN23" s="1">
-        <v>46090.37291666667</v>
+        <v>45964</v>
       </c>
       <c r="AO23" s="1">
-        <v>46139.45763888889</v>
+        <v>46034.66180555556</v>
       </c>
       <c r="AP23" s="1">
-        <v>46365.464583333334</v>
-      </c>
-      <c r="AU23" s="1">
-        <v>45958</v>
+        <v>46237.083333333336</v>
       </c>
       <c r="AV23" t="str">
         <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
       </c>
       <c r="AW23" t="str">
-        <v>Stéphanie HUGOT</v>
-      </c>
-      <c r="AX23" s="1">
-        <v>45953</v>
-      </c>
-      <c r="AY23" t="str">
-        <v>shugot@aefavl.fr</v>
-      </c>
-      <c r="AZ23" t="str">
-        <v>0320109220</v>
+        <v>Salim ZEGAOUI</v>
       </c>
       <c r="BA23" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="BB23" t="str">
-        <v>CARLIER</v>
-      </c>
-      <c r="BC23" t="str">
-        <v>Aurélie</v>
-      </c>
-      <c r="BD23" t="str">
-        <v>12 Rue des Murets 59280 ARMENTIERES</v>
-      </c>
-      <c r="BE23" t="str">
-        <v>0618860243</v>
-      </c>
-      <c r="BF23" t="str">
-        <v>acarlier@guydemarle.fr</v>
+        <v>NON</v>
       </c>
       <c r="BG23" t="str">
-        <v>11308</v>
-      </c>
-      <c r="BH23" s="1">
-        <v>45902.083333333336</v>
-      </c>
-      <c r="BI23" t="str">
-        <v>5934041V</v>
+        <v>597072</v>
       </c>
       <c r="BJ23" t="str">
-        <v>254b48c8-2e3d-4094-8a07-1ed39da282ef</v>
+        <v>d1e2bb85-dc1c-437d-8f9a-a1204114762b</v>
       </c>
       <c r="BK23" t="str">
         <v>Accepted</v>
@@ -4138,1728 +4114,15 @@
         <v/>
       </c>
       <c r="BM23" t="str">
-        <v>derenoncourt59@gmail.com</v>
+        <v/>
       </c>
       <c r="BN23" t="str">
-        <v>https://e2cgrandlille-my.sharepoint.com/:f:/g/personal/e_derenoncourt_e2c-grandlille_fr/IgCLIdvf00CSR4dh4PDg3FYHAT3Z7inSqHuHJU3jAuVQw5U?e=6czFdy</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>55646</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C24" t="str">
-        <v>BOUTIN</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Stella</v>
-      </c>
-      <c r="E24" t="str">
-        <v>s.boutin@e2c-grandlille.fr</v>
-      </c>
-      <c r="F24" t="str">
-        <v>0634167405</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I24" t="str">
-        <v>Employé / Employée de libre-service</v>
-      </c>
-      <c r="K24" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L24" t="str">
-        <v>référés Gérard</v>
-      </c>
-      <c r="M24" t="str">
-        <v>2602/février 2026 ARM</v>
-      </c>
-      <c r="O24" t="str">
-        <v>NOWINSKI Gérard</v>
-      </c>
-      <c r="P24">
-        <v>18</v>
-      </c>
-      <c r="Q24">
-        <v>18</v>
-      </c>
-      <c r="R24" s="1">
-        <v>39256</v>
-      </c>
-      <c r="T24" t="str">
-        <v>Armentières, FRANCE</v>
-      </c>
-      <c r="U24" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V24" t="str">
-        <v>OUI</v>
-      </c>
-      <c r="W24" t="str">
-        <v>72 Route d'Estaires</v>
-      </c>
-      <c r="X24" t="str">
-        <v>59660</v>
-      </c>
-      <c r="Y24" t="str">
-        <v>Merville</v>
-      </c>
-      <c r="Z24" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB24" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC24" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD24" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE24" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF24" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG24" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH24" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI24" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ24" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK24" t="str">
-        <v>153h45m</v>
-      </c>
-      <c r="AL24" t="str">
-        <v>216h</v>
-      </c>
-      <c r="AM24" t="str">
-        <v>186h</v>
-      </c>
-      <c r="AN24" s="1">
-        <v>46055.652083333334</v>
-      </c>
-      <c r="AO24" s="1">
-        <v>46139.46256944445</v>
-      </c>
-      <c r="AP24" s="1">
-        <v>46328.34097222222</v>
-      </c>
-      <c r="AU24" s="1">
-        <v>45995</v>
-      </c>
-      <c r="AV24" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW24" t="str">
-        <v>Antoine DERYCKERE</v>
-      </c>
-      <c r="AX24" s="1">
-        <v>45995</v>
-      </c>
-      <c r="AY24" t="str">
-        <v>aderyckere@aefavl.fr</v>
-      </c>
-      <c r="AZ24" t="str">
-        <v>0320109220</v>
-      </c>
-      <c r="BA24" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG24" t="str">
-        <v>9993</v>
-      </c>
-      <c r="BH24" s="1">
-        <v>45658.041666666664</v>
-      </c>
-      <c r="BI24" t="str">
-        <v>5876450W</v>
-      </c>
-      <c r="BJ24" t="str">
-        <v>771f1ecf-e2b8-4bf9-be3b-f3c69c2bac41</v>
-      </c>
-      <c r="BK24" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL24" t="str">
-        <v/>
-      </c>
-      <c r="BM24" t="str">
-        <v/>
-      </c>
-      <c r="BN24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>55151</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C25" t="str">
-        <v>LESAGE</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Perrine</v>
-      </c>
-      <c r="E25" t="str">
-        <v>plucie26@icloud.com</v>
-      </c>
-      <c r="F25" t="str">
-        <v>0656898509</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I25" t="str">
-        <v>Agent / Agente de service hospitalier (ASH)</v>
-      </c>
-      <c r="K25" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L25" t="str">
-        <v>référés Coralie</v>
-      </c>
-      <c r="M25" t="str">
-        <v>2511/novembre 2025 ARM</v>
-      </c>
-      <c r="O25" t="str">
-        <v>BENKHALIL Coralie</v>
-      </c>
-      <c r="P25">
-        <v>18</v>
-      </c>
-      <c r="Q25">
-        <v>17</v>
-      </c>
-      <c r="R25" s="1">
-        <v>39412</v>
-      </c>
-      <c r="T25" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="U25" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W25" t="str">
-        <v>9 9 Rue De la Cité</v>
-      </c>
-      <c r="X25" t="str">
-        <v>5980</v>
-      </c>
-      <c r="Y25" t="str">
-        <v>ARMENTIERES</v>
-      </c>
-      <c r="Z25" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB25" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC25" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD25" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE25" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF25" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG25" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH25" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI25" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ25" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK25" t="str">
-        <v>301h15m</v>
-      </c>
-      <c r="AL25" t="str">
-        <v>170h</v>
-      </c>
-      <c r="AM25" t="str">
-        <v>235h45m</v>
-      </c>
-      <c r="AN25" s="1">
-        <v>45964</v>
-      </c>
-      <c r="AO25" s="1">
-        <v>46034.635416666664</v>
-      </c>
-      <c r="AP25" s="1">
-        <v>46237.083333333336</v>
-      </c>
-      <c r="AV25" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW25" t="str">
-        <v>Salim ZEGAOUI</v>
-      </c>
-      <c r="BA25" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BB25" t="str">
-        <v>Cathy Villabessais 07/83/57/38/25 villabessaiscathy@gmail.com</v>
-      </c>
-      <c r="BG25" t="str">
-        <v>597073</v>
-      </c>
-      <c r="BJ25" t="str">
-        <v>563a8417-57ad-49bb-8c9b-24d83d16b55c</v>
-      </c>
-      <c r="BK25" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL25" t="str">
-        <v/>
-      </c>
-      <c r="BM25" t="str">
-        <v/>
-      </c>
-      <c r="BN25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>55123</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C26" t="str">
-        <v>REUBRECHT</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Elina</v>
-      </c>
-      <c r="E26" t="str">
-        <v>elinareubrecht8@gmail.com</v>
-      </c>
-      <c r="F26" t="str">
-        <v>0607541573</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I26" t="str">
-        <v>Auxiliaire de puériculture</v>
-      </c>
-      <c r="K26" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L26" t="str">
-        <v>référés Coralie</v>
-      </c>
-      <c r="M26" t="str">
-        <v>2510/octobre 2025 ARM</v>
-      </c>
-      <c r="O26" t="str">
-        <v>BENKHALIL Coralie</v>
-      </c>
-      <c r="P26">
-        <v>16</v>
-      </c>
-      <c r="Q26">
-        <v>16</v>
-      </c>
-      <c r="R26" s="1">
-        <v>39990</v>
-      </c>
-      <c r="T26" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="U26" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W26" t="str">
-        <v>25 25 Rue De l'Epargne</v>
-      </c>
-      <c r="X26" t="str">
-        <v>59280</v>
-      </c>
-      <c r="Y26" t="str">
-        <v>ARMENTIERES</v>
-      </c>
-      <c r="Z26" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB26" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC26" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD26" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE26" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF26" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG26" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH26" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI26" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ26" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK26" t="str">
-        <v>410h45m</v>
-      </c>
-      <c r="AL26" t="str">
-        <v>514h15m</v>
-      </c>
-      <c r="AM26" t="str">
-        <v>160h15m</v>
-      </c>
-      <c r="AN26" s="1">
-        <v>45931</v>
-      </c>
-      <c r="AO26" s="1">
-        <v>45982.041666666664</v>
-      </c>
-      <c r="AP26" s="1">
-        <v>46204.083333333336</v>
-      </c>
-      <c r="AV26" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW26" t="str">
-        <v>Salim ZEGAOUI</v>
-      </c>
-      <c r="BA26" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BB26" t="str">
-        <v>Marina Verhaeghe 06/12/38/63/84 marinaverhaeghe5@gmail.com Florine Seck, Educatrice Apprentis d'Auteuil 06/60/37/56/75</v>
-      </c>
-      <c r="BG26" t="str">
-        <v>595562</v>
-      </c>
-      <c r="BJ26" t="str">
-        <v>bbc0b065-efb0-4b95-b782-029d1fb2d74f</v>
-      </c>
-      <c r="BK26" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL26" t="str">
-        <v/>
-      </c>
-      <c r="BM26" t="str">
-        <v/>
-      </c>
-      <c r="BN26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>39970</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C27" t="str">
-        <v>ROUTARD</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Arone</v>
-      </c>
-      <c r="E27" t="str">
-        <v>arone.routard@gmail.com</v>
-      </c>
-      <c r="F27" t="str">
-        <v>0778438275</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="L27" t="str">
-        <v>référés Jérôme</v>
-      </c>
-      <c r="M27" t="str">
-        <v>2512/décembre 2025 ARM</v>
-      </c>
-      <c r="O27" t="str">
-        <v>BOLPAIRE Jérôme</v>
-      </c>
-      <c r="P27">
-        <v>19</v>
-      </c>
-      <c r="Q27">
-        <v>19</v>
-      </c>
-      <c r="R27" s="1">
-        <v>38982</v>
-      </c>
-      <c r="T27" t="str">
-        <v>Condé sur l'Escaut</v>
-      </c>
-      <c r="U27" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W27" t="str">
-        <v>24 24 Rue Du Comte d'Artois</v>
-      </c>
-      <c r="X27" t="str">
-        <v>59285</v>
-      </c>
-      <c r="Y27" t="str">
-        <v>ARNEKE</v>
-      </c>
-      <c r="Z27" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB27" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC27" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD27" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE27" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF27" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG27" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH27" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI27" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ27" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK27" t="str">
-        <v>308h15m</v>
-      </c>
-      <c r="AL27" t="str">
-        <v>288h30m</v>
-      </c>
-      <c r="AM27" t="str">
-        <v>114h30m</v>
-      </c>
-      <c r="AN27" s="1">
-        <v>46006</v>
-      </c>
-      <c r="AO27" s="1">
-        <v>46066.40833333333</v>
-      </c>
-      <c r="AP27" s="1">
-        <v>46280.083333333336</v>
-      </c>
-      <c r="AV27" t="str">
-        <v>MISSION LOCALE FLANDRE INTERIEURE - Antenne de Steenvoorde</v>
-      </c>
-      <c r="AW27" t="str">
-        <v>Ludivine KEDZIORA</v>
-      </c>
-      <c r="BA27" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG27" t="str">
-        <v>598064</v>
-      </c>
-      <c r="BJ27" t="str">
-        <v>e8028bb8-5ecd-4279-b986-83dd6331caf1</v>
-      </c>
-      <c r="BK27" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL27" t="str">
-        <v/>
-      </c>
-      <c r="BM27" t="str">
-        <v/>
-      </c>
-      <c r="BN27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>39967</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C28" t="str">
-        <v>PINCK--SOMON</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Océane</v>
-      </c>
-      <c r="E28" t="str">
-        <v>oceanesomon91@gmail.com</v>
-      </c>
-      <c r="F28" t="str">
-        <v>0664700478</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Aide-soignant / Aide-soignante</v>
-      </c>
-      <c r="K28" t="str">
-        <v>J'ai des idées</v>
-      </c>
-      <c r="L28" t="str">
-        <v>référés Coralie</v>
-      </c>
-      <c r="M28" t="str">
-        <v>2512/décembre 2025 ARM</v>
-      </c>
-      <c r="O28" t="str">
-        <v>BENKHALIL Coralie</v>
-      </c>
-      <c r="P28">
-        <v>18</v>
-      </c>
-      <c r="Q28">
-        <v>18</v>
-      </c>
-      <c r="R28" s="1">
-        <v>39305</v>
-      </c>
-      <c r="T28" t="str">
-        <v>Tourcoing</v>
-      </c>
-      <c r="U28" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W28" t="str">
-        <v>12 12 Rue Roland Garros</v>
-      </c>
-      <c r="X28" t="str">
-        <v>59280</v>
-      </c>
-      <c r="Y28" t="str">
-        <v>ARMENTIERES</v>
-      </c>
-      <c r="Z28" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB28" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC28" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD28" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE28" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF28" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG28" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH28" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI28" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ28" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK28" t="str">
-        <v>239h30m</v>
-      </c>
-      <c r="AL28" t="str">
-        <v>168h</v>
-      </c>
-      <c r="AM28" t="str">
-        <v>210h15m</v>
-      </c>
-      <c r="AN28" s="1">
-        <v>46006</v>
-      </c>
-      <c r="AO28" s="1">
-        <v>46101.60972222222</v>
-      </c>
-      <c r="AP28" s="1">
-        <v>46280.083333333336</v>
-      </c>
-      <c r="AV28" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW28" t="str">
-        <v>Salim ZEGAOUI</v>
-      </c>
-      <c r="BA28" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG28" t="str">
-        <v>598061</v>
-      </c>
-      <c r="BJ28" t="str">
-        <v>483024f2-edc4-467c-85a5-413bb74aa552</v>
-      </c>
-      <c r="BK28" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL28" t="str">
-        <v/>
-      </c>
-      <c r="BM28" t="str">
-        <v/>
-      </c>
-      <c r="BN28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>39966</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C29" t="str">
-        <v>BERNINI</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Lizéa</v>
-      </c>
-      <c r="E29" t="str">
-        <v>lizea.bernini@gmail.com</v>
-      </c>
-      <c r="F29" t="str">
-        <v>0630158880</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I29" t="str">
-        <v>Animateur / Animatrice d'atelier en maison de retraite</v>
-      </c>
-      <c r="K29" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L29" t="str">
-        <v>référés Delphine P.</v>
-      </c>
-      <c r="M29" t="str">
-        <v>2512/décembre 2025 ARM</v>
-      </c>
-      <c r="O29" t="str">
-        <v>PASQUIER Delphine</v>
-      </c>
-      <c r="P29">
-        <v>20</v>
-      </c>
-      <c r="Q29">
-        <v>19</v>
-      </c>
-      <c r="R29" s="1">
-        <v>38790</v>
-      </c>
-      <c r="T29" t="str">
-        <v>Houplines</v>
-      </c>
-      <c r="U29" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W29" t="str">
-        <v>8 8 Rue Charles Baudelaire</v>
-      </c>
-      <c r="X29" t="str">
-        <v>59116</v>
-      </c>
-      <c r="Y29" t="str">
-        <v>HOUPLINES</v>
-      </c>
-      <c r="Z29" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB29" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC29" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
-      </c>
-      <c r="AD29" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE29" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF29" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG29" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH29" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI29" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ29" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK29" t="str">
-        <v>243h15m</v>
-      </c>
-      <c r="AL29" t="str">
-        <v>295h40m</v>
-      </c>
-      <c r="AM29" t="str">
-        <v>169h15m</v>
-      </c>
-      <c r="AN29" s="1">
-        <v>46006</v>
-      </c>
-      <c r="AO29" s="1">
-        <v>46070.347916666666</v>
-      </c>
-      <c r="AP29" s="1">
-        <v>46280.083333333336</v>
-      </c>
-      <c r="AV29" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW29" t="str">
-        <v>Manon DIEN</v>
-      </c>
-      <c r="BA29" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG29" t="str">
-        <v>598054</v>
-      </c>
-      <c r="BJ29" t="str">
-        <v>dbe3c094-a51f-4ade-b50e-2f2c24cad008</v>
-      </c>
-      <c r="BK29" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL29" t="str">
-        <v/>
-      </c>
-      <c r="BM29" t="str">
-        <v/>
-      </c>
-      <c r="BN29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>39964</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C30" t="str">
-        <v>BAUDELET</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Vivien</v>
-      </c>
-      <c r="E30" t="str">
-        <v>vivien.baudelet59840@gmail.com</v>
-      </c>
-      <c r="F30" t="str">
-        <v>0610533593</v>
-      </c>
-      <c r="G30" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Commis de cuisine tournant / Commise de cuisine tournante</v>
-      </c>
-      <c r="K30" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L30" t="str">
-        <v>référés Coralie</v>
-      </c>
-      <c r="M30" t="str">
-        <v>2512/décembre 2025 ARM</v>
-      </c>
-      <c r="O30" t="str">
-        <v>BENKHALIL Coralie</v>
-      </c>
-      <c r="P30">
-        <v>24</v>
-      </c>
-      <c r="Q30">
-        <v>23</v>
-      </c>
-      <c r="R30" s="1">
-        <v>37252</v>
-      </c>
-      <c r="T30" t="str">
-        <v>Amiens</v>
-      </c>
-      <c r="U30" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W30" t="str">
-        <v>37 37 Rue Victor Hugo Bât 304B</v>
-      </c>
-      <c r="X30" t="str">
-        <v>59116</v>
-      </c>
-      <c r="Y30" t="str">
-        <v>HOUPLINES</v>
-      </c>
-      <c r="Z30" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB30" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC30" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD30" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE30" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF30" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG30" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH30" t="str">
-        <v>Oui</v>
-      </c>
-      <c r="AI30" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ30" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK30" t="str">
-        <v>349h30m</v>
-      </c>
-      <c r="AL30" t="str">
-        <v>291h30m</v>
-      </c>
-      <c r="AM30" t="str">
-        <v>54h45m</v>
-      </c>
-      <c r="AN30" s="1">
-        <v>46006</v>
-      </c>
-      <c r="AO30" s="1">
-        <v>46066.40833333333</v>
-      </c>
-      <c r="AP30" s="1">
-        <v>46280.083333333336</v>
-      </c>
-      <c r="AV30" t="str">
-        <v>En direct</v>
-      </c>
-      <c r="BA30" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG30" t="str">
-        <v>598052</v>
-      </c>
-      <c r="BJ30" t="str">
-        <v>78db74bf-aef8-401d-a236-6b0643e4fde4</v>
-      </c>
-      <c r="BK30" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL30" t="str">
-        <v/>
-      </c>
-      <c r="BM30" t="str">
-        <v/>
-      </c>
-      <c r="BN30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>39963</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C31" t="str">
-        <v>CALLEWAERT</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Kenny</v>
-      </c>
-      <c r="E31" t="str">
-        <v>kenny-callewaert@hotmail.com</v>
-      </c>
-      <c r="F31" t="str">
-        <v>0644889275</v>
-      </c>
-      <c r="G31" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I31" t="str">
-        <v>Vendeur / Vendeuse en accessoires automobile</v>
-      </c>
-      <c r="K31" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L31" t="str">
-        <v>référés Jérôme</v>
-      </c>
-      <c r="M31" t="str">
-        <v>2512/décembre 2025 ARM</v>
-      </c>
-      <c r="O31" t="str">
-        <v>BOLPAIRE Jérôme</v>
-      </c>
-      <c r="P31">
-        <v>23</v>
-      </c>
-      <c r="Q31">
-        <v>23</v>
-      </c>
-      <c r="R31" s="1">
-        <v>37482</v>
-      </c>
-      <c r="T31" t="str">
-        <v>Lomme</v>
-      </c>
-      <c r="U31" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="W31" t="str">
-        <v>5 5 Avenue De la Libération</v>
-      </c>
-      <c r="X31" t="str">
-        <v>59043</v>
-      </c>
-      <c r="Y31" t="str">
-        <v>BAILLEUL</v>
-      </c>
-      <c r="Z31" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB31" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC31" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD31" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE31" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF31" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG31" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH31" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI31" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ31" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK31" t="str">
-        <v>391h45m</v>
-      </c>
-      <c r="AL31" t="str">
-        <v>266h30m</v>
-      </c>
-      <c r="AM31" t="str">
-        <v>41h45m</v>
-      </c>
-      <c r="AN31" s="1">
-        <v>46006</v>
-      </c>
-      <c r="AO31" s="1">
-        <v>46066.40902777778</v>
-      </c>
-      <c r="AP31" s="1">
-        <v>46280.083333333336</v>
-      </c>
-      <c r="AV31" t="str">
-        <v>MISSION LOCALE DE FLANDRE INTERIEURE</v>
-      </c>
-      <c r="AW31" t="str">
-        <v>Odile DEWYNTER</v>
-      </c>
-      <c r="BA31" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG31" t="str">
-        <v>412402</v>
-      </c>
-      <c r="BJ31" t="str">
-        <v>bc397cbe-0371-4147-9451-dce0bb1c1e97</v>
-      </c>
-      <c r="BK31" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL31" t="str">
-        <v/>
-      </c>
-      <c r="BM31" t="str">
-        <v/>
-      </c>
-      <c r="BN31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>36687</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C32" t="str">
-        <v>LANDAS</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Kimberley</v>
-      </c>
-      <c r="E32" t="str">
-        <v>landas.kimberley@gmail.com</v>
-      </c>
-      <c r="F32" t="str">
-        <v>0614742515</v>
-      </c>
-      <c r="G32" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H32" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I32" t="str">
-        <v>Assistant / Assistante accueil petite enfance</v>
-      </c>
-      <c r="K32" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L32" t="str">
-        <v>référés Delphine P.</v>
-      </c>
-      <c r="M32" t="str">
-        <v>2511/novembre 2025 ARM</v>
-      </c>
-      <c r="O32" t="str">
-        <v>PASQUIER Delphine</v>
-      </c>
-      <c r="P32">
-        <v>18</v>
-      </c>
-      <c r="Q32">
-        <v>17</v>
-      </c>
-      <c r="R32" s="1">
-        <v>39401</v>
-      </c>
-      <c r="T32" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="U32" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V32" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W32" t="str">
-        <v>23 23 Rue Félix Faure</v>
-      </c>
-      <c r="X32" t="str">
-        <v>59280</v>
-      </c>
-      <c r="Y32" t="str">
-        <v>ARMENTIERES</v>
-      </c>
-      <c r="Z32" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB32" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC32" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD32" t="str">
-        <v>3 validé</v>
-      </c>
-      <c r="AE32" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF32" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG32" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH32" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI32" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ32" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK32" t="str">
-        <v>489h30m</v>
-      </c>
-      <c r="AL32" t="str">
-        <v>229h45m</v>
-      </c>
-      <c r="AM32" t="str">
-        <v>60h</v>
-      </c>
-      <c r="AN32" s="1">
-        <v>45964</v>
-      </c>
-      <c r="AO32" s="1">
-        <v>46034.66180555556</v>
-      </c>
-      <c r="AP32" s="1">
-        <v>46237.083333333336</v>
-      </c>
-      <c r="AV32" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW32" t="str">
-        <v>Salim ZEGAOUI</v>
-      </c>
-      <c r="BA32" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG32" t="str">
-        <v>597072</v>
-      </c>
-      <c r="BJ32" t="str">
-        <v>d1e2bb85-dc1c-437d-8f9a-a1204114762b</v>
-      </c>
-      <c r="BK32" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL32" t="str">
-        <v/>
-      </c>
-      <c r="BM32" t="str">
-        <v/>
-      </c>
-      <c r="BN32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>35230</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Homme</v>
-      </c>
-      <c r="C33" t="str">
-        <v>HORTHEMEL</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="E33" t="str">
-        <v>tom.horthemel.22@gmail.com</v>
-      </c>
-      <c r="F33" t="str">
-        <v>0782890443</v>
-      </c>
-      <c r="G33" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H33" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I33" t="str">
-        <v>Agent / Agente d'accueil</v>
-      </c>
-      <c r="K33" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L33" t="str">
-        <v>référés Delphine P.</v>
-      </c>
-      <c r="M33" t="str">
-        <v>2510/octobre 2025 ARM</v>
-      </c>
-      <c r="O33" t="str">
-        <v>PASQUIER Delphine</v>
-      </c>
-      <c r="P33">
-        <v>22</v>
-      </c>
-      <c r="Q33">
-        <v>21</v>
-      </c>
-      <c r="R33" s="1">
-        <v>38118</v>
-      </c>
-      <c r="T33" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="U33" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V33" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W33" t="str">
-        <v>315 315 Rue Du Fief</v>
-      </c>
-      <c r="X33" t="str">
-        <v>62840</v>
-      </c>
-      <c r="Y33" t="str">
-        <v>SAILLY SUR LA LYS</v>
-      </c>
-      <c r="Z33" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB33" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC33" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD33" t="str">
-        <v>3 non validé</v>
-      </c>
-      <c r="AE33" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF33" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG33" t="str">
-        <v>AVEC</v>
-      </c>
-      <c r="AH33" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI33" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ33" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK33" t="str">
-        <v>539h30m</v>
-      </c>
-      <c r="AL33" t="str">
-        <v>360h</v>
-      </c>
-      <c r="AM33" t="str">
-        <v>68h</v>
-      </c>
-      <c r="AN33" s="1">
-        <v>45931</v>
-      </c>
-      <c r="AO33" s="1">
-        <v>45982.041666666664</v>
-      </c>
-      <c r="AP33" s="1">
-        <v>46204.083333333336</v>
-      </c>
-      <c r="AV33" t="str">
-        <v>CAP EMPLOI</v>
-      </c>
-      <c r="AW33" t="str">
-        <v>Céline Braibant</v>
-      </c>
-      <c r="BA33" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG33" t="str">
-        <v>569525</v>
-      </c>
-      <c r="BJ33" t="str">
-        <v>f118774e-02ae-475d-8d4e-c0e9d523b67d</v>
-      </c>
-      <c r="BK33" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL33" t="str">
-        <v/>
-      </c>
-      <c r="BM33" t="str">
-        <v/>
-      </c>
-      <c r="BN33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>32961</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C34" t="str">
-        <v>POLLET</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Margot</v>
-      </c>
-      <c r="E34" t="str">
-        <v>margotpollet714@gmail.com</v>
-      </c>
-      <c r="F34" t="str">
-        <v>0787094707</v>
-      </c>
-      <c r="G34" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H34" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I34" t="str">
-        <v>Gendarme</v>
-      </c>
-      <c r="K34" t="str">
-        <v>J'y vais</v>
-      </c>
-      <c r="L34" t="str">
-        <v>référés Delphine P.</v>
-      </c>
-      <c r="M34" t="str">
-        <v>2509/septembre 2025 ARM</v>
-      </c>
-      <c r="O34" t="str">
-        <v>PASQUIER Delphine</v>
-      </c>
-      <c r="P34">
-        <v>18</v>
-      </c>
-      <c r="Q34">
-        <v>17</v>
-      </c>
-      <c r="R34" s="1">
-        <v>39598</v>
-      </c>
-      <c r="T34" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="U34" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V34" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W34" t="str">
-        <v>38 38 Rue Emilienne Moreau</v>
-      </c>
-      <c r="X34" t="str">
-        <v>59280</v>
-      </c>
-      <c r="Y34" t="str">
-        <v>ARMENTIERES</v>
-      </c>
-      <c r="Z34" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB34" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC34" t="str">
-        <v>NON</v>
-      </c>
-      <c r="AD34" t="str">
-        <v>3 non validé</v>
-      </c>
-      <c r="AE34" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF34" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG34" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH34" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI34" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ34" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK34" t="str">
-        <v>592h</v>
-      </c>
-      <c r="AL34" t="str">
-        <v>451h</v>
-      </c>
-      <c r="AM34" t="str">
-        <v>65h45m</v>
-      </c>
-      <c r="AN34" s="1">
-        <v>45901</v>
-      </c>
-      <c r="AO34" s="1">
-        <v>45940.083333333336</v>
-      </c>
-      <c r="AP34" s="1">
-        <v>46174.083333333336</v>
-      </c>
-      <c r="AV34" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW34" t="str">
-        <v>Salim ZEGAOUI</v>
-      </c>
-      <c r="BA34" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BB34" t="str">
-        <v>Véronique Pollet 06/30/90/91/68 pollet.veronique.72@gmail.com</v>
-      </c>
-      <c r="BG34" t="str">
-        <v>594307</v>
-      </c>
-      <c r="BJ34" t="str">
-        <v>4efcfdae-3e5e-417f-99db-6c66b6c47f9d</v>
-      </c>
-      <c r="BK34" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL34" t="str">
-        <v/>
-      </c>
-      <c r="BM34" t="str">
-        <v/>
-      </c>
-      <c r="BN34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>32956</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Femme</v>
-      </c>
-      <c r="C35" t="str">
-        <v>CORRAO</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Gabriella</v>
-      </c>
-      <c r="E35" t="str">
-        <v>gabriela085959@gmail.com</v>
-      </c>
-      <c r="F35" t="str">
-        <v>0602490153</v>
-      </c>
-      <c r="G35" t="str">
-        <v>Grand Lille</v>
-      </c>
-      <c r="H35" t="str">
-        <v>Armentières</v>
-      </c>
-      <c r="I35" t="str">
-        <v>Aide-soignant / Aide-soignante</v>
-      </c>
-      <c r="K35" t="str">
-        <v>Je sais</v>
-      </c>
-      <c r="L35" t="str">
-        <v>référés Gérard</v>
-      </c>
-      <c r="M35" t="str">
-        <v>2509/septembre 2025 ARM</v>
-      </c>
-      <c r="O35" t="str">
-        <v>NOWINSKI Gérard</v>
-      </c>
-      <c r="P35">
-        <v>18</v>
-      </c>
-      <c r="Q35">
-        <v>17</v>
-      </c>
-      <c r="R35" s="1">
-        <v>39500</v>
-      </c>
-      <c r="T35" t="str">
-        <v>Lille</v>
-      </c>
-      <c r="U35" t="str">
-        <v>FRANCAISE</v>
-      </c>
-      <c r="V35" t="str">
-        <v>NON</v>
-      </c>
-      <c r="W35" t="str">
-        <v>1 1 Rue Maréchal Joffre Entrée 1 Appt 131</v>
-      </c>
-      <c r="X35" t="str">
-        <v>59280</v>
-      </c>
-      <c r="Y35" t="str">
-        <v>ARMENTIERES</v>
-      </c>
-      <c r="Z35" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AB35" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AC35" t="str">
-        <v>CEJ_MISSION_LOCALE</v>
-      </c>
-      <c r="AD35" t="str">
-        <v>Infra 3</v>
-      </c>
-      <c r="AE35" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AF35" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AG35" t="str">
-        <v>SANS</v>
-      </c>
-      <c r="AH35" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AI35" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AJ35" t="str">
-        <v>Non</v>
-      </c>
-      <c r="AK35" t="str">
-        <v>328h15m</v>
-      </c>
-      <c r="AL35" t="str">
-        <v>302h</v>
-      </c>
-      <c r="AM35" t="str">
-        <v>52h</v>
-      </c>
-      <c r="AN35" s="1">
-        <v>45901</v>
-      </c>
-      <c r="AO35" s="1">
-        <v>45940.083333333336</v>
-      </c>
-      <c r="AP35" s="1">
-        <v>46174.083333333336</v>
-      </c>
-      <c r="AV35" t="str">
-        <v>MISSION LOCALE ARMENTIERES-VALLEE DE LA LYS</v>
-      </c>
-      <c r="AW35" t="str">
-        <v>Salim ZEGAOUI</v>
-      </c>
-      <c r="BA35" t="str">
-        <v>NON</v>
-      </c>
-      <c r="BG35" t="str">
-        <v>594304</v>
-      </c>
-      <c r="BJ35" t="str">
-        <v>654362fd-276c-41b0-adfd-21935eda85e5</v>
-      </c>
-      <c r="BK35" t="str">
-        <v>Accepted</v>
-      </c>
-      <c r="BL35" t="str">
-        <v/>
-      </c>
-      <c r="BM35" t="str">
-        <v/>
-      </c>
-      <c r="BN35" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BN35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BN23"/>
   </ignoredErrors>
 </worksheet>
 </file>